--- a/Sales_Analytics_Dashboard.xlsx
+++ b/Sales_Analytics_Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales_Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Region_Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category_Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly_Trend" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sales_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Region_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Category_Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Monthly_Trend" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sales_Data'!$A$1:$K$601</definedName>
@@ -27,16 +27,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -56,7 +53,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -64,23 +61,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -161,14 +149,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -192,7 +180,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -220,8 +208,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -247,8 +235,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -274,14 +262,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="13"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -304,14 +292,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -339,8 +327,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -366,8 +354,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -393,7 +381,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -401,16 +389,16 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="2520000"/>
+    <ext cx="5400000" cy="2700000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -420,7 +408,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -428,16 +416,16 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="2520000"/>
+    <ext cx="5400000" cy="2700000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -752,57 +740,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Order_ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Order_Date</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Customer_ID</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Units_Sold</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Unit_Price_INR</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Discount_Rate</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Sales_INR</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Profit_INR</t>
         </is>
@@ -814,7 +802,7 @@
           <t>ORD-00381</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="3" t="n">
         <v>45659</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -859,7 +847,7 @@
           <t>ORD-00104</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="3" t="n">
         <v>45660</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -904,7 +892,7 @@
           <t>ORD-00575</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="3" t="n">
         <v>45660</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +937,7 @@
           <t>ORD-00465</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="3" t="n">
         <v>45660</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,7 +982,7 @@
           <t>ORD-00303</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="3" t="n">
         <v>45661</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -1039,7 +1027,7 @@
           <t>ORD-00410</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="3" t="n">
         <v>45663</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -1084,7 +1072,7 @@
           <t>ORD-00478</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="3" t="n">
         <v>45664</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -1129,7 +1117,7 @@
           <t>ORD-00415</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="3" t="n">
         <v>45664</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -1174,7 +1162,7 @@
           <t>ORD-00300</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="3" t="n">
         <v>45665</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -1219,7 +1207,7 @@
           <t>ORD-00233</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="3" t="n">
         <v>45665</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -1264,7 +1252,7 @@
           <t>ORD-00540</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="3" t="n">
         <v>45665</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -1309,7 +1297,7 @@
           <t>ORD-00170</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="3" t="n">
         <v>45666</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -1354,7 +1342,7 @@
           <t>ORD-00272</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="3" t="n">
         <v>45666</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -1399,7 +1387,7 @@
           <t>ORD-00369</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="3" t="n">
         <v>45666</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -1444,7 +1432,7 @@
           <t>ORD-00429</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="3" t="n">
         <v>45667</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -1489,7 +1477,7 @@
           <t>ORD-00454</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="3" t="n">
         <v>45667</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1534,7 +1522,7 @@
           <t>ORD-00138</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="3" t="n">
         <v>45669</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1579,7 +1567,7 @@
           <t>ORD-00385</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="3" t="n">
         <v>45669</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1624,7 +1612,7 @@
           <t>ORD-00147</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="3" t="n">
         <v>45670</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -1669,7 +1657,7 @@
           <t>ORD-00117</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="3" t="n">
         <v>45671</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -1714,7 +1702,7 @@
           <t>ORD-00328</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="3" t="n">
         <v>45671</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -1759,7 +1747,7 @@
           <t>ORD-00250</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="3" t="n">
         <v>45673</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -1804,7 +1792,7 @@
           <t>ORD-00562</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="3" t="n">
         <v>45673</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1849,7 +1837,7 @@
           <t>ORD-00056</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="3" t="n">
         <v>45673</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -1894,7 +1882,7 @@
           <t>ORD-00352</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="3" t="n">
         <v>45674</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -1939,7 +1927,7 @@
           <t>ORD-00397</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" s="3" t="n">
         <v>45674</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -1984,7 +1972,7 @@
           <t>ORD-00574</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="3" t="n">
         <v>45675</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -2029,7 +2017,7 @@
           <t>ORD-00584</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="3" t="n">
         <v>45676</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -2074,7 +2062,7 @@
           <t>ORD-00546</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="3" t="n">
         <v>45677</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -2119,7 +2107,7 @@
           <t>ORD-00542</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="3" t="n">
         <v>45678</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -2164,7 +2152,7 @@
           <t>ORD-00150</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="3" t="n">
         <v>45679</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -2209,7 +2197,7 @@
           <t>ORD-00279</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="3" t="n">
         <v>45681</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -2254,7 +2242,7 @@
           <t>ORD-00036</t>
         </is>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="3" t="n">
         <v>45681</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -2299,7 +2287,7 @@
           <t>ORD-00045</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n">
+      <c r="B35" s="3" t="n">
         <v>45682</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -2344,7 +2332,7 @@
           <t>ORD-00518</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="3" t="n">
         <v>45682</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -2389,7 +2377,7 @@
           <t>ORD-00387</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n">
+      <c r="B37" s="3" t="n">
         <v>45682</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -2434,7 +2422,7 @@
           <t>ORD-00069</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n">
+      <c r="B38" s="3" t="n">
         <v>45685</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -2479,7 +2467,7 @@
           <t>ORD-00217</t>
         </is>
       </c>
-      <c r="B39" s="4" t="n">
+      <c r="B39" s="3" t="n">
         <v>45686</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -2524,7 +2512,7 @@
           <t>ORD-00127</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n">
+      <c r="B40" s="3" t="n">
         <v>45686</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -2569,7 +2557,7 @@
           <t>ORD-00439</t>
         </is>
       </c>
-      <c r="B41" s="4" t="n">
+      <c r="B41" s="3" t="n">
         <v>45687</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -2614,7 +2602,7 @@
           <t>ORD-00431</t>
         </is>
       </c>
-      <c r="B42" s="4" t="n">
+      <c r="B42" s="3" t="n">
         <v>45688</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -2659,7 +2647,7 @@
           <t>ORD-00246</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n">
+      <c r="B43" s="3" t="n">
         <v>45688</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -2704,7 +2692,7 @@
           <t>ORD-00280</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n">
+      <c r="B44" s="3" t="n">
         <v>45688</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -2749,7 +2737,7 @@
           <t>ORD-00007</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n">
+      <c r="B45" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -2794,7 +2782,7 @@
           <t>ORD-00196</t>
         </is>
       </c>
-      <c r="B46" s="4" t="n">
+      <c r="B46" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -2839,7 +2827,7 @@
           <t>ORD-00172</t>
         </is>
       </c>
-      <c r="B47" s="4" t="n">
+      <c r="B47" s="3" t="n">
         <v>45690</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -2884,7 +2872,7 @@
           <t>ORD-00001</t>
         </is>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B48" s="3" t="n">
         <v>45690</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -2929,7 +2917,7 @@
           <t>ORD-00133</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n">
+      <c r="B49" s="3" t="n">
         <v>45691</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -2974,7 +2962,7 @@
           <t>ORD-00359</t>
         </is>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="B50" s="3" t="n">
         <v>45691</v>
       </c>
       <c r="C50" t="inlineStr">
@@ -3019,7 +3007,7 @@
           <t>ORD-00033</t>
         </is>
       </c>
-      <c r="B51" s="4" t="n">
+      <c r="B51" s="3" t="n">
         <v>45691</v>
       </c>
       <c r="C51" t="inlineStr">
@@ -3064,7 +3052,7 @@
           <t>ORD-00243</t>
         </is>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="B52" s="3" t="n">
         <v>45692</v>
       </c>
       <c r="C52" t="inlineStr">
@@ -3109,7 +3097,7 @@
           <t>ORD-00376</t>
         </is>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="B53" s="3" t="n">
         <v>45692</v>
       </c>
       <c r="C53" t="inlineStr">
@@ -3154,7 +3142,7 @@
           <t>ORD-00010</t>
         </is>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" s="3" t="n">
         <v>45692</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -3199,7 +3187,7 @@
           <t>ORD-00581</t>
         </is>
       </c>
-      <c r="B55" s="4" t="n">
+      <c r="B55" s="3" t="n">
         <v>45692</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -3244,7 +3232,7 @@
           <t>ORD-00087</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n">
+      <c r="B56" s="3" t="n">
         <v>45693</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -3289,7 +3277,7 @@
           <t>ORD-00218</t>
         </is>
       </c>
-      <c r="B57" s="4" t="n">
+      <c r="B57" s="3" t="n">
         <v>45693</v>
       </c>
       <c r="C57" t="inlineStr">
@@ -3334,7 +3322,7 @@
           <t>ORD-00588</t>
         </is>
       </c>
-      <c r="B58" s="4" t="n">
+      <c r="B58" s="3" t="n">
         <v>45694</v>
       </c>
       <c r="C58" t="inlineStr">
@@ -3379,7 +3367,7 @@
           <t>ORD-00580</t>
         </is>
       </c>
-      <c r="B59" s="4" t="n">
+      <c r="B59" s="3" t="n">
         <v>45695</v>
       </c>
       <c r="C59" t="inlineStr">
@@ -3424,7 +3412,7 @@
           <t>ORD-00258</t>
         </is>
       </c>
-      <c r="B60" s="4" t="n">
+      <c r="B60" s="3" t="n">
         <v>45695</v>
       </c>
       <c r="C60" t="inlineStr">
@@ -3469,7 +3457,7 @@
           <t>ORD-00583</t>
         </is>
       </c>
-      <c r="B61" s="4" t="n">
+      <c r="B61" s="3" t="n">
         <v>45696</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -3514,7 +3502,7 @@
           <t>ORD-00171</t>
         </is>
       </c>
-      <c r="B62" s="4" t="n">
+      <c r="B62" s="3" t="n">
         <v>45696</v>
       </c>
       <c r="C62" t="inlineStr">
@@ -3559,7 +3547,7 @@
           <t>ORD-00460</t>
         </is>
       </c>
-      <c r="B63" s="4" t="n">
+      <c r="B63" s="3" t="n">
         <v>45696</v>
       </c>
       <c r="C63" t="inlineStr">
@@ -3604,7 +3592,7 @@
           <t>ORD-00516</t>
         </is>
       </c>
-      <c r="B64" s="4" t="n">
+      <c r="B64" s="3" t="n">
         <v>45696</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -3649,7 +3637,7 @@
           <t>ORD-00322</t>
         </is>
       </c>
-      <c r="B65" s="4" t="n">
+      <c r="B65" s="3" t="n">
         <v>45697</v>
       </c>
       <c r="C65" t="inlineStr">
@@ -3694,7 +3682,7 @@
           <t>ORD-00310</t>
         </is>
       </c>
-      <c r="B66" s="4" t="n">
+      <c r="B66" s="3" t="n">
         <v>45697</v>
       </c>
       <c r="C66" t="inlineStr">
@@ -3739,7 +3727,7 @@
           <t>ORD-00480</t>
         </is>
       </c>
-      <c r="B67" s="4" t="n">
+      <c r="B67" s="3" t="n">
         <v>45697</v>
       </c>
       <c r="C67" t="inlineStr">
@@ -3784,7 +3772,7 @@
           <t>ORD-00501</t>
         </is>
       </c>
-      <c r="B68" s="4" t="n">
+      <c r="B68" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="C68" t="inlineStr">
@@ -3829,7 +3817,7 @@
           <t>ORD-00120</t>
         </is>
       </c>
-      <c r="B69" s="4" t="n">
+      <c r="B69" s="3" t="n">
         <v>45699</v>
       </c>
       <c r="C69" t="inlineStr">
@@ -3874,7 +3862,7 @@
           <t>ORD-00365</t>
         </is>
       </c>
-      <c r="B70" s="4" t="n">
+      <c r="B70" s="3" t="n">
         <v>45700</v>
       </c>
       <c r="C70" t="inlineStr">
@@ -3919,7 +3907,7 @@
           <t>ORD-00538</t>
         </is>
       </c>
-      <c r="B71" s="4" t="n">
+      <c r="B71" s="3" t="n">
         <v>45700</v>
       </c>
       <c r="C71" t="inlineStr">
@@ -3964,7 +3952,7 @@
           <t>ORD-00497</t>
         </is>
       </c>
-      <c r="B72" s="4" t="n">
+      <c r="B72" s="3" t="n">
         <v>45701</v>
       </c>
       <c r="C72" t="inlineStr">
@@ -4009,7 +3997,7 @@
           <t>ORD-00198</t>
         </is>
       </c>
-      <c r="B73" s="4" t="n">
+      <c r="B73" s="3" t="n">
         <v>45701</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -4054,7 +4042,7 @@
           <t>ORD-00313</t>
         </is>
       </c>
-      <c r="B74" s="4" t="n">
+      <c r="B74" s="3" t="n">
         <v>45701</v>
       </c>
       <c r="C74" t="inlineStr">
@@ -4099,7 +4087,7 @@
           <t>ORD-00386</t>
         </is>
       </c>
-      <c r="B75" s="4" t="n">
+      <c r="B75" s="3" t="n">
         <v>45702</v>
       </c>
       <c r="C75" t="inlineStr">
@@ -4144,7 +4132,7 @@
           <t>ORD-00418</t>
         </is>
       </c>
-      <c r="B76" s="4" t="n">
+      <c r="B76" s="3" t="n">
         <v>45702</v>
       </c>
       <c r="C76" t="inlineStr">
@@ -4189,7 +4177,7 @@
           <t>ORD-00436</t>
         </is>
       </c>
-      <c r="B77" s="4" t="n">
+      <c r="B77" s="3" t="n">
         <v>45703</v>
       </c>
       <c r="C77" t="inlineStr">
@@ -4234,7 +4222,7 @@
           <t>ORD-00221</t>
         </is>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B78" s="3" t="n">
         <v>45704</v>
       </c>
       <c r="C78" t="inlineStr">
@@ -4279,7 +4267,7 @@
           <t>ORD-00157</t>
         </is>
       </c>
-      <c r="B79" s="4" t="n">
+      <c r="B79" s="3" t="n">
         <v>45704</v>
       </c>
       <c r="C79" t="inlineStr">
@@ -4324,7 +4312,7 @@
           <t>ORD-00018</t>
         </is>
       </c>
-      <c r="B80" s="4" t="n">
+      <c r="B80" s="3" t="n">
         <v>45704</v>
       </c>
       <c r="C80" t="inlineStr">
@@ -4369,7 +4357,7 @@
           <t>ORD-00434</t>
         </is>
       </c>
-      <c r="B81" s="4" t="n">
+      <c r="B81" s="3" t="n">
         <v>45705</v>
       </c>
       <c r="C81" t="inlineStr">
@@ -4414,7 +4402,7 @@
           <t>ORD-00074</t>
         </is>
       </c>
-      <c r="B82" s="4" t="n">
+      <c r="B82" s="3" t="n">
         <v>45705</v>
       </c>
       <c r="C82" t="inlineStr">
@@ -4459,7 +4447,7 @@
           <t>ORD-00443</t>
         </is>
       </c>
-      <c r="B83" s="4" t="n">
+      <c r="B83" s="3" t="n">
         <v>45706</v>
       </c>
       <c r="C83" t="inlineStr">
@@ -4504,7 +4492,7 @@
           <t>ORD-00414</t>
         </is>
       </c>
-      <c r="B84" s="4" t="n">
+      <c r="B84" s="3" t="n">
         <v>45706</v>
       </c>
       <c r="C84" t="inlineStr">
@@ -4549,7 +4537,7 @@
           <t>ORD-00118</t>
         </is>
       </c>
-      <c r="B85" s="4" t="n">
+      <c r="B85" s="3" t="n">
         <v>45709</v>
       </c>
       <c r="C85" t="inlineStr">
@@ -4594,7 +4582,7 @@
           <t>ORD-00462</t>
         </is>
       </c>
-      <c r="B86" s="4" t="n">
+      <c r="B86" s="3" t="n">
         <v>45709</v>
       </c>
       <c r="C86" t="inlineStr">
@@ -4639,7 +4627,7 @@
           <t>ORD-00100</t>
         </is>
       </c>
-      <c r="B87" s="4" t="n">
+      <c r="B87" s="3" t="n">
         <v>45709</v>
       </c>
       <c r="C87" t="inlineStr">
@@ -4684,7 +4672,7 @@
           <t>ORD-00306</t>
         </is>
       </c>
-      <c r="B88" s="4" t="n">
+      <c r="B88" s="3" t="n">
         <v>45709</v>
       </c>
       <c r="C88" t="inlineStr">
@@ -4729,7 +4717,7 @@
           <t>ORD-00241</t>
         </is>
       </c>
-      <c r="B89" s="4" t="n">
+      <c r="B89" s="3" t="n">
         <v>45709</v>
       </c>
       <c r="C89" t="inlineStr">
@@ -4774,7 +4762,7 @@
           <t>ORD-00329</t>
         </is>
       </c>
-      <c r="B90" s="4" t="n">
+      <c r="B90" s="3" t="n">
         <v>45709</v>
       </c>
       <c r="C90" t="inlineStr">
@@ -4819,7 +4807,7 @@
           <t>ORD-00528</t>
         </is>
       </c>
-      <c r="B91" s="4" t="n">
+      <c r="B91" s="3" t="n">
         <v>45710</v>
       </c>
       <c r="C91" t="inlineStr">
@@ -4864,7 +4852,7 @@
           <t>ORD-00408</t>
         </is>
       </c>
-      <c r="B92" s="4" t="n">
+      <c r="B92" s="3" t="n">
         <v>45710</v>
       </c>
       <c r="C92" t="inlineStr">
@@ -4909,7 +4897,7 @@
           <t>ORD-00256</t>
         </is>
       </c>
-      <c r="B93" s="4" t="n">
+      <c r="B93" s="3" t="n">
         <v>45710</v>
       </c>
       <c r="C93" t="inlineStr">
@@ -4954,7 +4942,7 @@
           <t>ORD-00522</t>
         </is>
       </c>
-      <c r="B94" s="4" t="n">
+      <c r="B94" s="3" t="n">
         <v>45711</v>
       </c>
       <c r="C94" t="inlineStr">
@@ -4999,7 +4987,7 @@
           <t>ORD-00457</t>
         </is>
       </c>
-      <c r="B95" s="4" t="n">
+      <c r="B95" s="3" t="n">
         <v>45712</v>
       </c>
       <c r="C95" t="inlineStr">
@@ -5044,7 +5032,7 @@
           <t>ORD-00182</t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B96" s="3" t="n">
         <v>45713</v>
       </c>
       <c r="C96" t="inlineStr">
@@ -5089,7 +5077,7 @@
           <t>ORD-00273</t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B97" s="3" t="n">
         <v>45713</v>
       </c>
       <c r="C97" t="inlineStr">
@@ -5134,7 +5122,7 @@
           <t>ORD-00357</t>
         </is>
       </c>
-      <c r="B98" s="4" t="n">
+      <c r="B98" s="3" t="n">
         <v>45713</v>
       </c>
       <c r="C98" t="inlineStr">
@@ -5179,7 +5167,7 @@
           <t>ORD-00390</t>
         </is>
       </c>
-      <c r="B99" s="4" t="n">
+      <c r="B99" s="3" t="n">
         <v>45713</v>
       </c>
       <c r="C99" t="inlineStr">
@@ -5224,7 +5212,7 @@
           <t>ORD-00533</t>
         </is>
       </c>
-      <c r="B100" s="4" t="n">
+      <c r="B100" s="3" t="n">
         <v>45714</v>
       </c>
       <c r="C100" t="inlineStr">
@@ -5269,7 +5257,7 @@
           <t>ORD-00536</t>
         </is>
       </c>
-      <c r="B101" s="4" t="n">
+      <c r="B101" s="3" t="n">
         <v>45714</v>
       </c>
       <c r="C101" t="inlineStr">
@@ -5314,7 +5302,7 @@
           <t>ORD-00058</t>
         </is>
       </c>
-      <c r="B102" s="4" t="n">
+      <c r="B102" s="3" t="n">
         <v>45714</v>
       </c>
       <c r="C102" t="inlineStr">
@@ -5359,7 +5347,7 @@
           <t>ORD-00178</t>
         </is>
       </c>
-      <c r="B103" s="4" t="n">
+      <c r="B103" s="3" t="n">
         <v>45716</v>
       </c>
       <c r="C103" t="inlineStr">
@@ -5404,7 +5392,7 @@
           <t>ORD-00287</t>
         </is>
       </c>
-      <c r="B104" s="4" t="n">
+      <c r="B104" s="3" t="n">
         <v>45716</v>
       </c>
       <c r="C104" t="inlineStr">
@@ -5449,7 +5437,7 @@
           <t>ORD-00083</t>
         </is>
       </c>
-      <c r="B105" s="4" t="n">
+      <c r="B105" s="3" t="n">
         <v>45716</v>
       </c>
       <c r="C105" t="inlineStr">
@@ -5494,7 +5482,7 @@
           <t>ORD-00168</t>
         </is>
       </c>
-      <c r="B106" s="4" t="n">
+      <c r="B106" s="3" t="n">
         <v>45718</v>
       </c>
       <c r="C106" t="inlineStr">
@@ -5539,7 +5527,7 @@
           <t>ORD-00467</t>
         </is>
       </c>
-      <c r="B107" s="4" t="n">
+      <c r="B107" s="3" t="n">
         <v>45718</v>
       </c>
       <c r="C107" t="inlineStr">
@@ -5584,7 +5572,7 @@
           <t>ORD-00532</t>
         </is>
       </c>
-      <c r="B108" s="4" t="n">
+      <c r="B108" s="3" t="n">
         <v>45718</v>
       </c>
       <c r="C108" t="inlineStr">
@@ -5629,7 +5617,7 @@
           <t>ORD-00041</t>
         </is>
       </c>
-      <c r="B109" s="4" t="n">
+      <c r="B109" s="3" t="n">
         <v>45718</v>
       </c>
       <c r="C109" t="inlineStr">
@@ -5674,7 +5662,7 @@
           <t>ORD-00350</t>
         </is>
       </c>
-      <c r="B110" s="4" t="n">
+      <c r="B110" s="3" t="n">
         <v>45718</v>
       </c>
       <c r="C110" t="inlineStr">
@@ -5719,7 +5707,7 @@
           <t>ORD-00187</t>
         </is>
       </c>
-      <c r="B111" s="4" t="n">
+      <c r="B111" s="3" t="n">
         <v>45718</v>
       </c>
       <c r="C111" t="inlineStr">
@@ -5764,7 +5752,7 @@
           <t>ORD-00262</t>
         </is>
       </c>
-      <c r="B112" s="4" t="n">
+      <c r="B112" s="3" t="n">
         <v>45720</v>
       </c>
       <c r="C112" t="inlineStr">
@@ -5809,7 +5797,7 @@
           <t>ORD-00411</t>
         </is>
       </c>
-      <c r="B113" s="4" t="n">
+      <c r="B113" s="3" t="n">
         <v>45721</v>
       </c>
       <c r="C113" t="inlineStr">
@@ -5854,7 +5842,7 @@
           <t>ORD-00259</t>
         </is>
       </c>
-      <c r="B114" s="4" t="n">
+      <c r="B114" s="3" t="n">
         <v>45721</v>
       </c>
       <c r="C114" t="inlineStr">
@@ -5899,7 +5887,7 @@
           <t>ORD-00544</t>
         </is>
       </c>
-      <c r="B115" s="4" t="n">
+      <c r="B115" s="3" t="n">
         <v>45721</v>
       </c>
       <c r="C115" t="inlineStr">
@@ -5944,7 +5932,7 @@
           <t>ORD-00230</t>
         </is>
       </c>
-      <c r="B116" s="4" t="n">
+      <c r="B116" s="3" t="n">
         <v>45722</v>
       </c>
       <c r="C116" t="inlineStr">
@@ -5989,7 +5977,7 @@
           <t>ORD-00251</t>
         </is>
       </c>
-      <c r="B117" s="4" t="n">
+      <c r="B117" s="3" t="n">
         <v>45723</v>
       </c>
       <c r="C117" t="inlineStr">
@@ -6034,7 +6022,7 @@
           <t>ORD-00349</t>
         </is>
       </c>
-      <c r="B118" s="4" t="n">
+      <c r="B118" s="3" t="n">
         <v>45723</v>
       </c>
       <c r="C118" t="inlineStr">
@@ -6079,7 +6067,7 @@
           <t>ORD-00392</t>
         </is>
       </c>
-      <c r="B119" s="4" t="n">
+      <c r="B119" s="3" t="n">
         <v>45723</v>
       </c>
       <c r="C119" t="inlineStr">
@@ -6124,7 +6112,7 @@
           <t>ORD-00469</t>
         </is>
       </c>
-      <c r="B120" s="4" t="n">
+      <c r="B120" s="3" t="n">
         <v>45724</v>
       </c>
       <c r="C120" t="inlineStr">
@@ -6169,7 +6157,7 @@
           <t>ORD-00023</t>
         </is>
       </c>
-      <c r="B121" s="4" t="n">
+      <c r="B121" s="3" t="n">
         <v>45724</v>
       </c>
       <c r="C121" t="inlineStr">
@@ -6214,7 +6202,7 @@
           <t>ORD-00564</t>
         </is>
       </c>
-      <c r="B122" s="4" t="n">
+      <c r="B122" s="3" t="n">
         <v>45724</v>
       </c>
       <c r="C122" t="inlineStr">
@@ -6259,7 +6247,7 @@
           <t>ORD-00253</t>
         </is>
       </c>
-      <c r="B123" s="4" t="n">
+      <c r="B123" s="3" t="n">
         <v>45726</v>
       </c>
       <c r="C123" t="inlineStr">
@@ -6304,7 +6292,7 @@
           <t>ORD-00072</t>
         </is>
       </c>
-      <c r="B124" s="4" t="n">
+      <c r="B124" s="3" t="n">
         <v>45727</v>
       </c>
       <c r="C124" t="inlineStr">
@@ -6349,7 +6337,7 @@
           <t>ORD-00523</t>
         </is>
       </c>
-      <c r="B125" s="4" t="n">
+      <c r="B125" s="3" t="n">
         <v>45728</v>
       </c>
       <c r="C125" t="inlineStr">
@@ -6394,7 +6382,7 @@
           <t>ORD-00543</t>
         </is>
       </c>
-      <c r="B126" s="4" t="n">
+      <c r="B126" s="3" t="n">
         <v>45729</v>
       </c>
       <c r="C126" t="inlineStr">
@@ -6439,7 +6427,7 @@
           <t>ORD-00052</t>
         </is>
       </c>
-      <c r="B127" s="4" t="n">
+      <c r="B127" s="3" t="n">
         <v>45729</v>
       </c>
       <c r="C127" t="inlineStr">
@@ -6484,7 +6472,7 @@
           <t>ORD-00398</t>
         </is>
       </c>
-      <c r="B128" s="4" t="n">
+      <c r="B128" s="3" t="n">
         <v>45729</v>
       </c>
       <c r="C128" t="inlineStr">
@@ -6529,7 +6517,7 @@
           <t>ORD-00426</t>
         </is>
       </c>
-      <c r="B129" s="4" t="n">
+      <c r="B129" s="3" t="n">
         <v>45730</v>
       </c>
       <c r="C129" t="inlineStr">
@@ -6574,7 +6562,7 @@
           <t>ORD-00102</t>
         </is>
       </c>
-      <c r="B130" s="4" t="n">
+      <c r="B130" s="3" t="n">
         <v>45730</v>
       </c>
       <c r="C130" t="inlineStr">
@@ -6619,7 +6607,7 @@
           <t>ORD-00224</t>
         </is>
       </c>
-      <c r="B131" s="4" t="n">
+      <c r="B131" s="3" t="n">
         <v>45731</v>
       </c>
       <c r="C131" t="inlineStr">
@@ -6664,7 +6652,7 @@
           <t>ORD-00009</t>
         </is>
       </c>
-      <c r="B132" s="4" t="n">
+      <c r="B132" s="3" t="n">
         <v>45731</v>
       </c>
       <c r="C132" t="inlineStr">
@@ -6709,7 +6697,7 @@
           <t>ORD-00339</t>
         </is>
       </c>
-      <c r="B133" s="4" t="n">
+      <c r="B133" s="3" t="n">
         <v>45731</v>
       </c>
       <c r="C133" t="inlineStr">
@@ -6754,7 +6742,7 @@
           <t>ORD-00142</t>
         </is>
       </c>
-      <c r="B134" s="4" t="n">
+      <c r="B134" s="3" t="n">
         <v>45736</v>
       </c>
       <c r="C134" t="inlineStr">
@@ -6799,7 +6787,7 @@
           <t>ORD-00363</t>
         </is>
       </c>
-      <c r="B135" s="4" t="n">
+      <c r="B135" s="3" t="n">
         <v>45739</v>
       </c>
       <c r="C135" t="inlineStr">
@@ -6844,7 +6832,7 @@
           <t>ORD-00078</t>
         </is>
       </c>
-      <c r="B136" s="4" t="n">
+      <c r="B136" s="3" t="n">
         <v>45740</v>
       </c>
       <c r="C136" t="inlineStr">
@@ -6889,7 +6877,7 @@
           <t>ORD-00032</t>
         </is>
       </c>
-      <c r="B137" s="4" t="n">
+      <c r="B137" s="3" t="n">
         <v>45740</v>
       </c>
       <c r="C137" t="inlineStr">
@@ -6934,7 +6922,7 @@
           <t>ORD-00567</t>
         </is>
       </c>
-      <c r="B138" s="4" t="n">
+      <c r="B138" s="3" t="n">
         <v>45741</v>
       </c>
       <c r="C138" t="inlineStr">
@@ -6979,7 +6967,7 @@
           <t>ORD-00412</t>
         </is>
       </c>
-      <c r="B139" s="4" t="n">
+      <c r="B139" s="3" t="n">
         <v>45741</v>
       </c>
       <c r="C139" t="inlineStr">
@@ -7024,7 +7012,7 @@
           <t>ORD-00326</t>
         </is>
       </c>
-      <c r="B140" s="4" t="n">
+      <c r="B140" s="3" t="n">
         <v>45742</v>
       </c>
       <c r="C140" t="inlineStr">
@@ -7069,7 +7057,7 @@
           <t>ORD-00486</t>
         </is>
       </c>
-      <c r="B141" s="4" t="n">
+      <c r="B141" s="3" t="n">
         <v>45742</v>
       </c>
       <c r="C141" t="inlineStr">
@@ -7114,7 +7102,7 @@
           <t>ORD-00148</t>
         </is>
       </c>
-      <c r="B142" s="4" t="n">
+      <c r="B142" s="3" t="n">
         <v>45743</v>
       </c>
       <c r="C142" t="inlineStr">
@@ -7159,7 +7147,7 @@
           <t>ORD-00510</t>
         </is>
       </c>
-      <c r="B143" s="4" t="n">
+      <c r="B143" s="3" t="n">
         <v>45744</v>
       </c>
       <c r="C143" t="inlineStr">
@@ -7204,7 +7192,7 @@
           <t>ORD-00327</t>
         </is>
       </c>
-      <c r="B144" s="4" t="n">
+      <c r="B144" s="3" t="n">
         <v>45744</v>
       </c>
       <c r="C144" t="inlineStr">
@@ -7249,7 +7237,7 @@
           <t>ORD-00566</t>
         </is>
       </c>
-      <c r="B145" s="4" t="n">
+      <c r="B145" s="3" t="n">
         <v>45744</v>
       </c>
       <c r="C145" t="inlineStr">
@@ -7294,7 +7282,7 @@
           <t>ORD-00593</t>
         </is>
       </c>
-      <c r="B146" s="4" t="n">
+      <c r="B146" s="3" t="n">
         <v>45745</v>
       </c>
       <c r="C146" t="inlineStr">
@@ -7339,7 +7327,7 @@
           <t>ORD-00189</t>
         </is>
       </c>
-      <c r="B147" s="4" t="n">
+      <c r="B147" s="3" t="n">
         <v>45745</v>
       </c>
       <c r="C147" t="inlineStr">
@@ -7384,7 +7372,7 @@
           <t>ORD-00384</t>
         </is>
       </c>
-      <c r="B148" s="4" t="n">
+      <c r="B148" s="3" t="n">
         <v>45745</v>
       </c>
       <c r="C148" t="inlineStr">
@@ -7429,7 +7417,7 @@
           <t>ORD-00097</t>
         </is>
       </c>
-      <c r="B149" s="4" t="n">
+      <c r="B149" s="3" t="n">
         <v>45745</v>
       </c>
       <c r="C149" t="inlineStr">
@@ -7474,7 +7462,7 @@
           <t>ORD-00315</t>
         </is>
       </c>
-      <c r="B150" s="4" t="n">
+      <c r="B150" s="3" t="n">
         <v>45747</v>
       </c>
       <c r="C150" t="inlineStr">
@@ -7519,7 +7507,7 @@
           <t>ORD-00119</t>
         </is>
       </c>
-      <c r="B151" s="4" t="n">
+      <c r="B151" s="3" t="n">
         <v>45747</v>
       </c>
       <c r="C151" t="inlineStr">
@@ -7564,7 +7552,7 @@
           <t>ORD-00508</t>
         </is>
       </c>
-      <c r="B152" s="4" t="n">
+      <c r="B152" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="C152" t="inlineStr">
@@ -7609,7 +7597,7 @@
           <t>ORD-00483</t>
         </is>
       </c>
-      <c r="B153" s="4" t="n">
+      <c r="B153" s="3" t="n">
         <v>45749</v>
       </c>
       <c r="C153" t="inlineStr">
@@ -7654,7 +7642,7 @@
           <t>ORD-00568</t>
         </is>
       </c>
-      <c r="B154" s="4" t="n">
+      <c r="B154" s="3" t="n">
         <v>45749</v>
       </c>
       <c r="C154" t="inlineStr">
@@ -7699,7 +7687,7 @@
           <t>ORD-00346</t>
         </is>
       </c>
-      <c r="B155" s="4" t="n">
+      <c r="B155" s="3" t="n">
         <v>45751</v>
       </c>
       <c r="C155" t="inlineStr">
@@ -7744,7 +7732,7 @@
           <t>ORD-00380</t>
         </is>
       </c>
-      <c r="B156" s="4" t="n">
+      <c r="B156" s="3" t="n">
         <v>45753</v>
       </c>
       <c r="C156" t="inlineStr">
@@ -7789,7 +7777,7 @@
           <t>ORD-00211</t>
         </is>
       </c>
-      <c r="B157" s="4" t="n">
+      <c r="B157" s="3" t="n">
         <v>45753</v>
       </c>
       <c r="C157" t="inlineStr">
@@ -7834,7 +7822,7 @@
           <t>ORD-00209</t>
         </is>
       </c>
-      <c r="B158" s="4" t="n">
+      <c r="B158" s="3" t="n">
         <v>45754</v>
       </c>
       <c r="C158" t="inlineStr">
@@ -7879,7 +7867,7 @@
           <t>ORD-00206</t>
         </is>
       </c>
-      <c r="B159" s="4" t="n">
+      <c r="B159" s="3" t="n">
         <v>45755</v>
       </c>
       <c r="C159" t="inlineStr">
@@ -7924,7 +7912,7 @@
           <t>ORD-00292</t>
         </is>
       </c>
-      <c r="B160" s="4" t="n">
+      <c r="B160" s="3" t="n">
         <v>45755</v>
       </c>
       <c r="C160" t="inlineStr">
@@ -7969,7 +7957,7 @@
           <t>ORD-00509</t>
         </is>
       </c>
-      <c r="B161" s="4" t="n">
+      <c r="B161" s="3" t="n">
         <v>45756</v>
       </c>
       <c r="C161" t="inlineStr">
@@ -8014,7 +8002,7 @@
           <t>ORD-00216</t>
         </is>
       </c>
-      <c r="B162" s="4" t="n">
+      <c r="B162" s="3" t="n">
         <v>45757</v>
       </c>
       <c r="C162" t="inlineStr">
@@ -8059,7 +8047,7 @@
           <t>ORD-00143</t>
         </is>
       </c>
-      <c r="B163" s="4" t="n">
+      <c r="B163" s="3" t="n">
         <v>45758</v>
       </c>
       <c r="C163" t="inlineStr">
@@ -8104,7 +8092,7 @@
           <t>ORD-00505</t>
         </is>
       </c>
-      <c r="B164" s="4" t="n">
+      <c r="B164" s="3" t="n">
         <v>45758</v>
       </c>
       <c r="C164" t="inlineStr">
@@ -8149,7 +8137,7 @@
           <t>ORD-00281</t>
         </is>
       </c>
-      <c r="B165" s="4" t="n">
+      <c r="B165" s="3" t="n">
         <v>45758</v>
       </c>
       <c r="C165" t="inlineStr">
@@ -8194,7 +8182,7 @@
           <t>ORD-00039</t>
         </is>
       </c>
-      <c r="B166" s="4" t="n">
+      <c r="B166" s="3" t="n">
         <v>45759</v>
       </c>
       <c r="C166" t="inlineStr">
@@ -8239,7 +8227,7 @@
           <t>ORD-00413</t>
         </is>
       </c>
-      <c r="B167" s="4" t="n">
+      <c r="B167" s="3" t="n">
         <v>45759</v>
       </c>
       <c r="C167" t="inlineStr">
@@ -8284,7 +8272,7 @@
           <t>ORD-00111</t>
         </is>
       </c>
-      <c r="B168" s="4" t="n">
+      <c r="B168" s="3" t="n">
         <v>45759</v>
       </c>
       <c r="C168" t="inlineStr">
@@ -8329,7 +8317,7 @@
           <t>ORD-00399</t>
         </is>
       </c>
-      <c r="B169" s="4" t="n">
+      <c r="B169" s="3" t="n">
         <v>45760</v>
       </c>
       <c r="C169" t="inlineStr">
@@ -8374,7 +8362,7 @@
           <t>ORD-00314</t>
         </is>
       </c>
-      <c r="B170" s="4" t="n">
+      <c r="B170" s="3" t="n">
         <v>45760</v>
       </c>
       <c r="C170" t="inlineStr">
@@ -8419,7 +8407,7 @@
           <t>ORD-00152</t>
         </is>
       </c>
-      <c r="B171" s="4" t="n">
+      <c r="B171" s="3" t="n">
         <v>45760</v>
       </c>
       <c r="C171" t="inlineStr">
@@ -8464,7 +8452,7 @@
           <t>ORD-00573</t>
         </is>
       </c>
-      <c r="B172" s="4" t="n">
+      <c r="B172" s="3" t="n">
         <v>45761</v>
       </c>
       <c r="C172" t="inlineStr">
@@ -8509,7 +8497,7 @@
           <t>ORD-00534</t>
         </is>
       </c>
-      <c r="B173" s="4" t="n">
+      <c r="B173" s="3" t="n">
         <v>45761</v>
       </c>
       <c r="C173" t="inlineStr">
@@ -8554,7 +8542,7 @@
           <t>ORD-00299</t>
         </is>
       </c>
-      <c r="B174" s="4" t="n">
+      <c r="B174" s="3" t="n">
         <v>45761</v>
       </c>
       <c r="C174" t="inlineStr">
@@ -8599,7 +8587,7 @@
           <t>ORD-00450</t>
         </is>
       </c>
-      <c r="B175" s="4" t="n">
+      <c r="B175" s="3" t="n">
         <v>45762</v>
       </c>
       <c r="C175" t="inlineStr">
@@ -8644,7 +8632,7 @@
           <t>ORD-00495</t>
         </is>
       </c>
-      <c r="B176" s="4" t="n">
+      <c r="B176" s="3" t="n">
         <v>45763</v>
       </c>
       <c r="C176" t="inlineStr">
@@ -8689,7 +8677,7 @@
           <t>ORD-00096</t>
         </is>
       </c>
-      <c r="B177" s="4" t="n">
+      <c r="B177" s="3" t="n">
         <v>45763</v>
       </c>
       <c r="C177" t="inlineStr">
@@ -8734,7 +8722,7 @@
           <t>ORD-00481</t>
         </is>
       </c>
-      <c r="B178" s="4" t="n">
+      <c r="B178" s="3" t="n">
         <v>45763</v>
       </c>
       <c r="C178" t="inlineStr">
@@ -8779,7 +8767,7 @@
           <t>ORD-00342</t>
         </is>
       </c>
-      <c r="B179" s="4" t="n">
+      <c r="B179" s="3" t="n">
         <v>45764</v>
       </c>
       <c r="C179" t="inlineStr">
@@ -8824,7 +8812,7 @@
           <t>ORD-00154</t>
         </is>
       </c>
-      <c r="B180" s="4" t="n">
+      <c r="B180" s="3" t="n">
         <v>45765</v>
       </c>
       <c r="C180" t="inlineStr">
@@ -8869,7 +8857,7 @@
           <t>ORD-00271</t>
         </is>
       </c>
-      <c r="B181" s="4" t="n">
+      <c r="B181" s="3" t="n">
         <v>45765</v>
       </c>
       <c r="C181" t="inlineStr">
@@ -8914,7 +8902,7 @@
           <t>ORD-00419</t>
         </is>
       </c>
-      <c r="B182" s="4" t="n">
+      <c r="B182" s="3" t="n">
         <v>45766</v>
       </c>
       <c r="C182" t="inlineStr">
@@ -8959,7 +8947,7 @@
           <t>ORD-00442</t>
         </is>
       </c>
-      <c r="B183" s="4" t="n">
+      <c r="B183" s="3" t="n">
         <v>45767</v>
       </c>
       <c r="C183" t="inlineStr">
@@ -9004,7 +8992,7 @@
           <t>ORD-00263</t>
         </is>
       </c>
-      <c r="B184" s="4" t="n">
+      <c r="B184" s="3" t="n">
         <v>45767</v>
       </c>
       <c r="C184" t="inlineStr">
@@ -9049,7 +9037,7 @@
           <t>ORD-00353</t>
         </is>
       </c>
-      <c r="B185" s="4" t="n">
+      <c r="B185" s="3" t="n">
         <v>45767</v>
       </c>
       <c r="C185" t="inlineStr">
@@ -9094,7 +9082,7 @@
           <t>ORD-00190</t>
         </is>
       </c>
-      <c r="B186" s="4" t="n">
+      <c r="B186" s="3" t="n">
         <v>45768</v>
       </c>
       <c r="C186" t="inlineStr">
@@ -9139,7 +9127,7 @@
           <t>ORD-00307</t>
         </is>
       </c>
-      <c r="B187" s="4" t="n">
+      <c r="B187" s="3" t="n">
         <v>45768</v>
       </c>
       <c r="C187" t="inlineStr">
@@ -9184,7 +9172,7 @@
           <t>ORD-00136</t>
         </is>
       </c>
-      <c r="B188" s="4" t="n">
+      <c r="B188" s="3" t="n">
         <v>45768</v>
       </c>
       <c r="C188" t="inlineStr">
@@ -9229,7 +9217,7 @@
           <t>ORD-00226</t>
         </is>
       </c>
-      <c r="B189" s="4" t="n">
+      <c r="B189" s="3" t="n">
         <v>45769</v>
       </c>
       <c r="C189" t="inlineStr">
@@ -9274,7 +9262,7 @@
           <t>ORD-00239</t>
         </is>
       </c>
-      <c r="B190" s="4" t="n">
+      <c r="B190" s="3" t="n">
         <v>45770</v>
       </c>
       <c r="C190" t="inlineStr">
@@ -9319,7 +9307,7 @@
           <t>ORD-00333</t>
         </is>
       </c>
-      <c r="B191" s="4" t="n">
+      <c r="B191" s="3" t="n">
         <v>45771</v>
       </c>
       <c r="C191" t="inlineStr">
@@ -9364,7 +9352,7 @@
           <t>ORD-00526</t>
         </is>
       </c>
-      <c r="B192" s="4" t="n">
+      <c r="B192" s="3" t="n">
         <v>45771</v>
       </c>
       <c r="C192" t="inlineStr">
@@ -9409,7 +9397,7 @@
           <t>ORD-00400</t>
         </is>
       </c>
-      <c r="B193" s="4" t="n">
+      <c r="B193" s="3" t="n">
         <v>45771</v>
       </c>
       <c r="C193" t="inlineStr">
@@ -9454,7 +9442,7 @@
           <t>ORD-00447</t>
         </is>
       </c>
-      <c r="B194" s="4" t="n">
+      <c r="B194" s="3" t="n">
         <v>45772</v>
       </c>
       <c r="C194" t="inlineStr">
@@ -9499,7 +9487,7 @@
           <t>ORD-00088</t>
         </is>
       </c>
-      <c r="B195" s="4" t="n">
+      <c r="B195" s="3" t="n">
         <v>45772</v>
       </c>
       <c r="C195" t="inlineStr">
@@ -9544,7 +9532,7 @@
           <t>ORD-00338</t>
         </is>
       </c>
-      <c r="B196" s="4" t="n">
+      <c r="B196" s="3" t="n">
         <v>45773</v>
       </c>
       <c r="C196" t="inlineStr">
@@ -9589,7 +9577,7 @@
           <t>ORD-00309</t>
         </is>
       </c>
-      <c r="B197" s="4" t="n">
+      <c r="B197" s="3" t="n">
         <v>45773</v>
       </c>
       <c r="C197" t="inlineStr">
@@ -9634,7 +9622,7 @@
           <t>ORD-00368</t>
         </is>
       </c>
-      <c r="B198" s="4" t="n">
+      <c r="B198" s="3" t="n">
         <v>45773</v>
       </c>
       <c r="C198" t="inlineStr">
@@ -9679,7 +9667,7 @@
           <t>ORD-00403</t>
         </is>
       </c>
-      <c r="B199" s="4" t="n">
+      <c r="B199" s="3" t="n">
         <v>45774</v>
       </c>
       <c r="C199" t="inlineStr">
@@ -9724,7 +9712,7 @@
           <t>ORD-00554</t>
         </is>
       </c>
-      <c r="B200" s="4" t="n">
+      <c r="B200" s="3" t="n">
         <v>45774</v>
       </c>
       <c r="C200" t="inlineStr">
@@ -9769,7 +9757,7 @@
           <t>ORD-00525</t>
         </is>
       </c>
-      <c r="B201" s="4" t="n">
+      <c r="B201" s="3" t="n">
         <v>45774</v>
       </c>
       <c r="C201" t="inlineStr">
@@ -9814,7 +9802,7 @@
           <t>ORD-00321</t>
         </is>
       </c>
-      <c r="B202" s="4" t="n">
+      <c r="B202" s="3" t="n">
         <v>45775</v>
       </c>
       <c r="C202" t="inlineStr">
@@ -9859,7 +9847,7 @@
           <t>ORD-00167</t>
         </is>
       </c>
-      <c r="B203" s="4" t="n">
+      <c r="B203" s="3" t="n">
         <v>45775</v>
       </c>
       <c r="C203" t="inlineStr">
@@ -9904,7 +9892,7 @@
           <t>ORD-00595</t>
         </is>
       </c>
-      <c r="B204" s="4" t="n">
+      <c r="B204" s="3" t="n">
         <v>45775</v>
       </c>
       <c r="C204" t="inlineStr">
@@ -9949,7 +9937,7 @@
           <t>ORD-00066</t>
         </is>
       </c>
-      <c r="B205" s="4" t="n">
+      <c r="B205" s="3" t="n">
         <v>45776</v>
       </c>
       <c r="C205" t="inlineStr">
@@ -9994,7 +9982,7 @@
           <t>ORD-00254</t>
         </is>
       </c>
-      <c r="B206" s="4" t="n">
+      <c r="B206" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="C206" t="inlineStr">
@@ -10039,7 +10027,7 @@
           <t>ORD-00077</t>
         </is>
       </c>
-      <c r="B207" s="4" t="n">
+      <c r="B207" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="C207" t="inlineStr">
@@ -10084,7 +10072,7 @@
           <t>ORD-00487</t>
         </is>
       </c>
-      <c r="B208" s="4" t="n">
+      <c r="B208" s="3" t="n">
         <v>45779</v>
       </c>
       <c r="C208" t="inlineStr">
@@ -10129,7 +10117,7 @@
           <t>ORD-00294</t>
         </is>
       </c>
-      <c r="B209" s="4" t="n">
+      <c r="B209" s="3" t="n">
         <v>45779</v>
       </c>
       <c r="C209" t="inlineStr">
@@ -10174,7 +10162,7 @@
           <t>ORD-00371</t>
         </is>
       </c>
-      <c r="B210" s="4" t="n">
+      <c r="B210" s="3" t="n">
         <v>45780</v>
       </c>
       <c r="C210" t="inlineStr">
@@ -10219,7 +10207,7 @@
           <t>ORD-00169</t>
         </is>
       </c>
-      <c r="B211" s="4" t="n">
+      <c r="B211" s="3" t="n">
         <v>45780</v>
       </c>
       <c r="C211" t="inlineStr">
@@ -10264,7 +10252,7 @@
           <t>ORD-00199</t>
         </is>
       </c>
-      <c r="B212" s="4" t="n">
+      <c r="B212" s="3" t="n">
         <v>45781</v>
       </c>
       <c r="C212" t="inlineStr">
@@ -10309,7 +10297,7 @@
           <t>ORD-00197</t>
         </is>
       </c>
-      <c r="B213" s="4" t="n">
+      <c r="B213" s="3" t="n">
         <v>45783</v>
       </c>
       <c r="C213" t="inlineStr">
@@ -10354,7 +10342,7 @@
           <t>ORD-00139</t>
         </is>
       </c>
-      <c r="B214" s="4" t="n">
+      <c r="B214" s="3" t="n">
         <v>45784</v>
       </c>
       <c r="C214" t="inlineStr">
@@ -10399,7 +10387,7 @@
           <t>ORD-00268</t>
         </is>
       </c>
-      <c r="B215" s="4" t="n">
+      <c r="B215" s="3" t="n">
         <v>45784</v>
       </c>
       <c r="C215" t="inlineStr">
@@ -10444,7 +10432,7 @@
           <t>ORD-00044</t>
         </is>
       </c>
-      <c r="B216" s="4" t="n">
+      <c r="B216" s="3" t="n">
         <v>45787</v>
       </c>
       <c r="C216" t="inlineStr">
@@ -10489,7 +10477,7 @@
           <t>ORD-00521</t>
         </is>
       </c>
-      <c r="B217" s="4" t="n">
+      <c r="B217" s="3" t="n">
         <v>45788</v>
       </c>
       <c r="C217" t="inlineStr">
@@ -10534,7 +10522,7 @@
           <t>ORD-00301</t>
         </is>
       </c>
-      <c r="B218" s="4" t="n">
+      <c r="B218" s="3" t="n">
         <v>45790</v>
       </c>
       <c r="C218" t="inlineStr">
@@ -10579,7 +10567,7 @@
           <t>ORD-00194</t>
         </is>
       </c>
-      <c r="B219" s="4" t="n">
+      <c r="B219" s="3" t="n">
         <v>45790</v>
       </c>
       <c r="C219" t="inlineStr">
@@ -10624,7 +10612,7 @@
           <t>ORD-00053</t>
         </is>
       </c>
-      <c r="B220" s="4" t="n">
+      <c r="B220" s="3" t="n">
         <v>45790</v>
       </c>
       <c r="C220" t="inlineStr">
@@ -10669,7 +10657,7 @@
           <t>ORD-00201</t>
         </is>
       </c>
-      <c r="B221" s="4" t="n">
+      <c r="B221" s="3" t="n">
         <v>45791</v>
       </c>
       <c r="C221" t="inlineStr">
@@ -10714,7 +10702,7 @@
           <t>ORD-00063</t>
         </is>
       </c>
-      <c r="B222" s="4" t="n">
+      <c r="B222" s="3" t="n">
         <v>45791</v>
       </c>
       <c r="C222" t="inlineStr">
@@ -10759,7 +10747,7 @@
           <t>ORD-00393</t>
         </is>
       </c>
-      <c r="B223" s="4" t="n">
+      <c r="B223" s="3" t="n">
         <v>45792</v>
       </c>
       <c r="C223" t="inlineStr">
@@ -10804,7 +10792,7 @@
           <t>ORD-00332</t>
         </is>
       </c>
-      <c r="B224" s="4" t="n">
+      <c r="B224" s="3" t="n">
         <v>45793</v>
       </c>
       <c r="C224" t="inlineStr">
@@ -10849,7 +10837,7 @@
           <t>ORD-00068</t>
         </is>
       </c>
-      <c r="B225" s="4" t="n">
+      <c r="B225" s="3" t="n">
         <v>45793</v>
       </c>
       <c r="C225" t="inlineStr">
@@ -10894,7 +10882,7 @@
           <t>ORD-00022</t>
         </is>
       </c>
-      <c r="B226" s="4" t="n">
+      <c r="B226" s="3" t="n">
         <v>45793</v>
       </c>
       <c r="C226" t="inlineStr">
@@ -10939,7 +10927,7 @@
           <t>ORD-00374</t>
         </is>
       </c>
-      <c r="B227" s="4" t="n">
+      <c r="B227" s="3" t="n">
         <v>45794</v>
       </c>
       <c r="C227" t="inlineStr">
@@ -10984,7 +10972,7 @@
           <t>ORD-00576</t>
         </is>
       </c>
-      <c r="B228" s="4" t="n">
+      <c r="B228" s="3" t="n">
         <v>45794</v>
       </c>
       <c r="C228" t="inlineStr">
@@ -11029,7 +11017,7 @@
           <t>ORD-00498</t>
         </is>
       </c>
-      <c r="B229" s="4" t="n">
+      <c r="B229" s="3" t="n">
         <v>45794</v>
       </c>
       <c r="C229" t="inlineStr">
@@ -11074,7 +11062,7 @@
           <t>ORD-00379</t>
         </is>
       </c>
-      <c r="B230" s="4" t="n">
+      <c r="B230" s="3" t="n">
         <v>45796</v>
       </c>
       <c r="C230" t="inlineStr">
@@ -11119,7 +11107,7 @@
           <t>ORD-00188</t>
         </is>
       </c>
-      <c r="B231" s="4" t="n">
+      <c r="B231" s="3" t="n">
         <v>45797</v>
       </c>
       <c r="C231" t="inlineStr">
@@ -11164,7 +11152,7 @@
           <t>ORD-00094</t>
         </is>
       </c>
-      <c r="B232" s="4" t="n">
+      <c r="B232" s="3" t="n">
         <v>45799</v>
       </c>
       <c r="C232" t="inlineStr">
@@ -11209,7 +11197,7 @@
           <t>ORD-00552</t>
         </is>
       </c>
-      <c r="B233" s="4" t="n">
+      <c r="B233" s="3" t="n">
         <v>45801</v>
       </c>
       <c r="C233" t="inlineStr">
@@ -11254,7 +11242,7 @@
           <t>ORD-00440</t>
         </is>
       </c>
-      <c r="B234" s="4" t="n">
+      <c r="B234" s="3" t="n">
         <v>45803</v>
       </c>
       <c r="C234" t="inlineStr">
@@ -11299,7 +11287,7 @@
           <t>ORD-00027</t>
         </is>
       </c>
-      <c r="B235" s="4" t="n">
+      <c r="B235" s="3" t="n">
         <v>45804</v>
       </c>
       <c r="C235" t="inlineStr">
@@ -11344,7 +11332,7 @@
           <t>ORD-00585</t>
         </is>
       </c>
-      <c r="B236" s="4" t="n">
+      <c r="B236" s="3" t="n">
         <v>45805</v>
       </c>
       <c r="C236" t="inlineStr">
@@ -11389,7 +11377,7 @@
           <t>ORD-00164</t>
         </is>
       </c>
-      <c r="B237" s="4" t="n">
+      <c r="B237" s="3" t="n">
         <v>45806</v>
       </c>
       <c r="C237" t="inlineStr">
@@ -11434,7 +11422,7 @@
           <t>ORD-00163</t>
         </is>
       </c>
-      <c r="B238" s="4" t="n">
+      <c r="B238" s="3" t="n">
         <v>45807</v>
       </c>
       <c r="C238" t="inlineStr">
@@ -11479,7 +11467,7 @@
           <t>ORD-00144</t>
         </is>
       </c>
-      <c r="B239" s="4" t="n">
+      <c r="B239" s="3" t="n">
         <v>45807</v>
       </c>
       <c r="C239" t="inlineStr">
@@ -11524,7 +11512,7 @@
           <t>ORD-00065</t>
         </is>
       </c>
-      <c r="B240" s="4" t="n">
+      <c r="B240" s="3" t="n">
         <v>45807</v>
       </c>
       <c r="C240" t="inlineStr">
@@ -11569,7 +11557,7 @@
           <t>ORD-00373</t>
         </is>
       </c>
-      <c r="B241" s="4" t="n">
+      <c r="B241" s="3" t="n">
         <v>45807</v>
       </c>
       <c r="C241" t="inlineStr">
@@ -11614,7 +11602,7 @@
           <t>ORD-00496</t>
         </is>
       </c>
-      <c r="B242" s="4" t="n">
+      <c r="B242" s="3" t="n">
         <v>45808</v>
       </c>
       <c r="C242" t="inlineStr">
@@ -11659,7 +11647,7 @@
           <t>ORD-00572</t>
         </is>
       </c>
-      <c r="B243" s="4" t="n">
+      <c r="B243" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="C243" t="inlineStr">
@@ -11704,7 +11692,7 @@
           <t>ORD-00248</t>
         </is>
       </c>
-      <c r="B244" s="4" t="n">
+      <c r="B244" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="C244" t="inlineStr">
@@ -11749,7 +11737,7 @@
           <t>ORD-00425</t>
         </is>
       </c>
-      <c r="B245" s="4" t="n">
+      <c r="B245" s="3" t="n">
         <v>45810</v>
       </c>
       <c r="C245" t="inlineStr">
@@ -11794,7 +11782,7 @@
           <t>ORD-00165</t>
         </is>
       </c>
-      <c r="B246" s="4" t="n">
+      <c r="B246" s="3" t="n">
         <v>45810</v>
       </c>
       <c r="C246" t="inlineStr">
@@ -11839,7 +11827,7 @@
           <t>ORD-00464</t>
         </is>
       </c>
-      <c r="B247" s="4" t="n">
+      <c r="B247" s="3" t="n">
         <v>45810</v>
       </c>
       <c r="C247" t="inlineStr">
@@ -11884,7 +11872,7 @@
           <t>ORD-00275</t>
         </is>
       </c>
-      <c r="B248" s="4" t="n">
+      <c r="B248" s="3" t="n">
         <v>45810</v>
       </c>
       <c r="C248" t="inlineStr">
@@ -11929,7 +11917,7 @@
           <t>ORD-00500</t>
         </is>
       </c>
-      <c r="B249" s="4" t="n">
+      <c r="B249" s="3" t="n">
         <v>45813</v>
       </c>
       <c r="C249" t="inlineStr">
@@ -11974,7 +11962,7 @@
           <t>ORD-00547</t>
         </is>
       </c>
-      <c r="B250" s="4" t="n">
+      <c r="B250" s="3" t="n">
         <v>45814</v>
       </c>
       <c r="C250" t="inlineStr">
@@ -12019,7 +12007,7 @@
           <t>ORD-00473</t>
         </is>
       </c>
-      <c r="B251" s="4" t="n">
+      <c r="B251" s="3" t="n">
         <v>45815</v>
       </c>
       <c r="C251" t="inlineStr">
@@ -12064,7 +12052,7 @@
           <t>ORD-00238</t>
         </is>
       </c>
-      <c r="B252" s="4" t="n">
+      <c r="B252" s="3" t="n">
         <v>45815</v>
       </c>
       <c r="C252" t="inlineStr">
@@ -12109,7 +12097,7 @@
           <t>ORD-00091</t>
         </is>
       </c>
-      <c r="B253" s="4" t="n">
+      <c r="B253" s="3" t="n">
         <v>45816</v>
       </c>
       <c r="C253" t="inlineStr">
@@ -12154,7 +12142,7 @@
           <t>ORD-00005</t>
         </is>
       </c>
-      <c r="B254" s="4" t="n">
+      <c r="B254" s="3" t="n">
         <v>45816</v>
       </c>
       <c r="C254" t="inlineStr">
@@ -12199,7 +12187,7 @@
           <t>ORD-00407</t>
         </is>
       </c>
-      <c r="B255" s="4" t="n">
+      <c r="B255" s="3" t="n">
         <v>45816</v>
       </c>
       <c r="C255" t="inlineStr">
@@ -12244,7 +12232,7 @@
           <t>ORD-00435</t>
         </is>
       </c>
-      <c r="B256" s="4" t="n">
+      <c r="B256" s="3" t="n">
         <v>45816</v>
       </c>
       <c r="C256" t="inlineStr">
@@ -12289,7 +12277,7 @@
           <t>ORD-00155</t>
         </is>
       </c>
-      <c r="B257" s="4" t="n">
+      <c r="B257" s="3" t="n">
         <v>45816</v>
       </c>
       <c r="C257" t="inlineStr">
@@ -12334,7 +12322,7 @@
           <t>ORD-00354</t>
         </is>
       </c>
-      <c r="B258" s="4" t="n">
+      <c r="B258" s="3" t="n">
         <v>45816</v>
       </c>
       <c r="C258" t="inlineStr">
@@ -12379,7 +12367,7 @@
           <t>ORD-00082</t>
         </is>
       </c>
-      <c r="B259" s="4" t="n">
+      <c r="B259" s="3" t="n">
         <v>45817</v>
       </c>
       <c r="C259" t="inlineStr">
@@ -12424,7 +12412,7 @@
           <t>ORD-00140</t>
         </is>
       </c>
-      <c r="B260" s="4" t="n">
+      <c r="B260" s="3" t="n">
         <v>45817</v>
       </c>
       <c r="C260" t="inlineStr">
@@ -12469,7 +12457,7 @@
           <t>ORD-00121</t>
         </is>
       </c>
-      <c r="B261" s="4" t="n">
+      <c r="B261" s="3" t="n">
         <v>45818</v>
       </c>
       <c r="C261" t="inlineStr">
@@ -12514,7 +12502,7 @@
           <t>ORD-00298</t>
         </is>
       </c>
-      <c r="B262" s="4" t="n">
+      <c r="B262" s="3" t="n">
         <v>45818</v>
       </c>
       <c r="C262" t="inlineStr">
@@ -12559,7 +12547,7 @@
           <t>ORD-00004</t>
         </is>
       </c>
-      <c r="B263" s="4" t="n">
+      <c r="B263" s="3" t="n">
         <v>45818</v>
       </c>
       <c r="C263" t="inlineStr">
@@ -12604,7 +12592,7 @@
           <t>ORD-00030</t>
         </is>
       </c>
-      <c r="B264" s="4" t="n">
+      <c r="B264" s="3" t="n">
         <v>45819</v>
       </c>
       <c r="C264" t="inlineStr">
@@ -12649,7 +12637,7 @@
           <t>ORD-00285</t>
         </is>
       </c>
-      <c r="B265" s="4" t="n">
+      <c r="B265" s="3" t="n">
         <v>45819</v>
       </c>
       <c r="C265" t="inlineStr">
@@ -12694,7 +12682,7 @@
           <t>ORD-00047</t>
         </is>
       </c>
-      <c r="B266" s="4" t="n">
+      <c r="B266" s="3" t="n">
         <v>45820</v>
       </c>
       <c r="C266" t="inlineStr">
@@ -12739,7 +12727,7 @@
           <t>ORD-00186</t>
         </is>
       </c>
-      <c r="B267" s="4" t="n">
+      <c r="B267" s="3" t="n">
         <v>45820</v>
       </c>
       <c r="C267" t="inlineStr">
@@ -12784,7 +12772,7 @@
           <t>ORD-00219</t>
         </is>
       </c>
-      <c r="B268" s="4" t="n">
+      <c r="B268" s="3" t="n">
         <v>45821</v>
       </c>
       <c r="C268" t="inlineStr">
@@ -12829,7 +12817,7 @@
           <t>ORD-00267</t>
         </is>
       </c>
-      <c r="B269" s="4" t="n">
+      <c r="B269" s="3" t="n">
         <v>45821</v>
       </c>
       <c r="C269" t="inlineStr">
@@ -12874,7 +12862,7 @@
           <t>ORD-00020</t>
         </is>
       </c>
-      <c r="B270" s="4" t="n">
+      <c r="B270" s="3" t="n">
         <v>45822</v>
       </c>
       <c r="C270" t="inlineStr">
@@ -12919,7 +12907,7 @@
           <t>ORD-00214</t>
         </is>
       </c>
-      <c r="B271" s="4" t="n">
+      <c r="B271" s="3" t="n">
         <v>45822</v>
       </c>
       <c r="C271" t="inlineStr">
@@ -12964,7 +12952,7 @@
           <t>ORD-00031</t>
         </is>
       </c>
-      <c r="B272" s="4" t="n">
+      <c r="B272" s="3" t="n">
         <v>45822</v>
       </c>
       <c r="C272" t="inlineStr">
@@ -13009,7 +12997,7 @@
           <t>ORD-00506</t>
         </is>
       </c>
-      <c r="B273" s="4" t="n">
+      <c r="B273" s="3" t="n">
         <v>45823</v>
       </c>
       <c r="C273" t="inlineStr">
@@ -13054,7 +13042,7 @@
           <t>ORD-00537</t>
         </is>
       </c>
-      <c r="B274" s="4" t="n">
+      <c r="B274" s="3" t="n">
         <v>45824</v>
       </c>
       <c r="C274" t="inlineStr">
@@ -13099,7 +13087,7 @@
           <t>ORD-00222</t>
         </is>
       </c>
-      <c r="B275" s="4" t="n">
+      <c r="B275" s="3" t="n">
         <v>45824</v>
       </c>
       <c r="C275" t="inlineStr">
@@ -13144,7 +13132,7 @@
           <t>ORD-00205</t>
         </is>
       </c>
-      <c r="B276" s="4" t="n">
+      <c r="B276" s="3" t="n">
         <v>45824</v>
       </c>
       <c r="C276" t="inlineStr">
@@ -13189,7 +13177,7 @@
           <t>ORD-00114</t>
         </is>
       </c>
-      <c r="B277" s="4" t="n">
+      <c r="B277" s="3" t="n">
         <v>45825</v>
       </c>
       <c r="C277" t="inlineStr">
@@ -13234,7 +13222,7 @@
           <t>ORD-00335</t>
         </is>
       </c>
-      <c r="B278" s="4" t="n">
+      <c r="B278" s="3" t="n">
         <v>45825</v>
       </c>
       <c r="C278" t="inlineStr">
@@ -13279,7 +13267,7 @@
           <t>ORD-00176</t>
         </is>
       </c>
-      <c r="B279" s="4" t="n">
+      <c r="B279" s="3" t="n">
         <v>45826</v>
       </c>
       <c r="C279" t="inlineStr">
@@ -13324,7 +13312,7 @@
           <t>ORD-00485</t>
         </is>
       </c>
-      <c r="B280" s="4" t="n">
+      <c r="B280" s="3" t="n">
         <v>45826</v>
       </c>
       <c r="C280" t="inlineStr">
@@ -13369,7 +13357,7 @@
           <t>ORD-00073</t>
         </is>
       </c>
-      <c r="B281" s="4" t="n">
+      <c r="B281" s="3" t="n">
         <v>45826</v>
       </c>
       <c r="C281" t="inlineStr">
@@ -13414,7 +13402,7 @@
           <t>ORD-00231</t>
         </is>
       </c>
-      <c r="B282" s="4" t="n">
+      <c r="B282" s="3" t="n">
         <v>45827</v>
       </c>
       <c r="C282" t="inlineStr">
@@ -13459,7 +13447,7 @@
           <t>ORD-00054</t>
         </is>
       </c>
-      <c r="B283" s="4" t="n">
+      <c r="B283" s="3" t="n">
         <v>45828</v>
       </c>
       <c r="C283" t="inlineStr">
@@ -13504,7 +13492,7 @@
           <t>ORD-00277</t>
         </is>
       </c>
-      <c r="B284" s="4" t="n">
+      <c r="B284" s="3" t="n">
         <v>45828</v>
       </c>
       <c r="C284" t="inlineStr">
@@ -13549,7 +13537,7 @@
           <t>ORD-00474</t>
         </is>
       </c>
-      <c r="B285" s="4" t="n">
+      <c r="B285" s="3" t="n">
         <v>45828</v>
       </c>
       <c r="C285" t="inlineStr">
@@ -13594,7 +13582,7 @@
           <t>ORD-00124</t>
         </is>
       </c>
-      <c r="B286" s="4" t="n">
+      <c r="B286" s="3" t="n">
         <v>45829</v>
       </c>
       <c r="C286" t="inlineStr">
@@ -13639,7 +13627,7 @@
           <t>ORD-00367</t>
         </is>
       </c>
-      <c r="B287" s="4" t="n">
+      <c r="B287" s="3" t="n">
         <v>45829</v>
       </c>
       <c r="C287" t="inlineStr">
@@ -13684,7 +13672,7 @@
           <t>ORD-00070</t>
         </is>
       </c>
-      <c r="B288" s="4" t="n">
+      <c r="B288" s="3" t="n">
         <v>45829</v>
       </c>
       <c r="C288" t="inlineStr">
@@ -13729,7 +13717,7 @@
           <t>ORD-00290</t>
         </is>
       </c>
-      <c r="B289" s="4" t="n">
+      <c r="B289" s="3" t="n">
         <v>45830</v>
       </c>
       <c r="C289" t="inlineStr">
@@ -13774,7 +13762,7 @@
           <t>ORD-00109</t>
         </is>
       </c>
-      <c r="B290" s="4" t="n">
+      <c r="B290" s="3" t="n">
         <v>45830</v>
       </c>
       <c r="C290" t="inlineStr">
@@ -13819,7 +13807,7 @@
           <t>ORD-00519</t>
         </is>
       </c>
-      <c r="B291" s="4" t="n">
+      <c r="B291" s="3" t="n">
         <v>45831</v>
       </c>
       <c r="C291" t="inlineStr">
@@ -13864,7 +13852,7 @@
           <t>ORD-00076</t>
         </is>
       </c>
-      <c r="B292" s="4" t="n">
+      <c r="B292" s="3" t="n">
         <v>45831</v>
       </c>
       <c r="C292" t="inlineStr">
@@ -13909,7 +13897,7 @@
           <t>ORD-00276</t>
         </is>
       </c>
-      <c r="B293" s="4" t="n">
+      <c r="B293" s="3" t="n">
         <v>45834</v>
       </c>
       <c r="C293" t="inlineStr">
@@ -13954,7 +13942,7 @@
           <t>ORD-00282</t>
         </is>
       </c>
-      <c r="B294" s="4" t="n">
+      <c r="B294" s="3" t="n">
         <v>45835</v>
       </c>
       <c r="C294" t="inlineStr">
@@ -13999,7 +13987,7 @@
           <t>ORD-00444</t>
         </is>
       </c>
-      <c r="B295" s="4" t="n">
+      <c r="B295" s="3" t="n">
         <v>45836</v>
       </c>
       <c r="C295" t="inlineStr">
@@ -14044,7 +14032,7 @@
           <t>ORD-00235</t>
         </is>
       </c>
-      <c r="B296" s="4" t="n">
+      <c r="B296" s="3" t="n">
         <v>45837</v>
       </c>
       <c r="C296" t="inlineStr">
@@ -14089,7 +14077,7 @@
           <t>ORD-00563</t>
         </is>
       </c>
-      <c r="B297" s="4" t="n">
+      <c r="B297" s="3" t="n">
         <v>45837</v>
       </c>
       <c r="C297" t="inlineStr">
@@ -14134,7 +14122,7 @@
           <t>ORD-00284</t>
         </is>
       </c>
-      <c r="B298" s="4" t="n">
+      <c r="B298" s="3" t="n">
         <v>45837</v>
       </c>
       <c r="C298" t="inlineStr">
@@ -14179,7 +14167,7 @@
           <t>ORD-00252</t>
         </is>
       </c>
-      <c r="B299" s="4" t="n">
+      <c r="B299" s="3" t="n">
         <v>45838</v>
       </c>
       <c r="C299" t="inlineStr">
@@ -14224,7 +14212,7 @@
           <t>ORD-00185</t>
         </is>
       </c>
-      <c r="B300" s="4" t="n">
+      <c r="B300" s="3" t="n">
         <v>45838</v>
       </c>
       <c r="C300" t="inlineStr">
@@ -14269,7 +14257,7 @@
           <t>ORD-00203</t>
         </is>
       </c>
-      <c r="B301" s="4" t="n">
+      <c r="B301" s="3" t="n">
         <v>45838</v>
       </c>
       <c r="C301" t="inlineStr">
@@ -14314,7 +14302,7 @@
           <t>ORD-00183</t>
         </is>
       </c>
-      <c r="B302" s="4" t="n">
+      <c r="B302" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="C302" t="inlineStr">
@@ -14359,7 +14347,7 @@
           <t>ORD-00055</t>
         </is>
       </c>
-      <c r="B303" s="4" t="n">
+      <c r="B303" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="C303" t="inlineStr">
@@ -14404,7 +14392,7 @@
           <t>ORD-00406</t>
         </is>
       </c>
-      <c r="B304" s="4" t="n">
+      <c r="B304" s="3" t="n">
         <v>45840</v>
       </c>
       <c r="C304" t="inlineStr">
@@ -14449,7 +14437,7 @@
           <t>ORD-00180</t>
         </is>
       </c>
-      <c r="B305" s="4" t="n">
+      <c r="B305" s="3" t="n">
         <v>45840</v>
       </c>
       <c r="C305" t="inlineStr">
@@ -14494,7 +14482,7 @@
           <t>ORD-00453</t>
         </is>
       </c>
-      <c r="B306" s="4" t="n">
+      <c r="B306" s="3" t="n">
         <v>45840</v>
       </c>
       <c r="C306" t="inlineStr">
@@ -14539,7 +14527,7 @@
           <t>ORD-00405</t>
         </is>
       </c>
-      <c r="B307" s="4" t="n">
+      <c r="B307" s="3" t="n">
         <v>45840</v>
       </c>
       <c r="C307" t="inlineStr">
@@ -14584,7 +14572,7 @@
           <t>ORD-00021</t>
         </is>
       </c>
-      <c r="B308" s="4" t="n">
+      <c r="B308" s="3" t="n">
         <v>45840</v>
       </c>
       <c r="C308" t="inlineStr">
@@ -14629,7 +14617,7 @@
           <t>ORD-00556</t>
         </is>
       </c>
-      <c r="B309" s="4" t="n">
+      <c r="B309" s="3" t="n">
         <v>45842</v>
       </c>
       <c r="C309" t="inlineStr">
@@ -14674,7 +14662,7 @@
           <t>ORD-00420</t>
         </is>
       </c>
-      <c r="B310" s="4" t="n">
+      <c r="B310" s="3" t="n">
         <v>45842</v>
       </c>
       <c r="C310" t="inlineStr">
@@ -14719,7 +14707,7 @@
           <t>ORD-00115</t>
         </is>
       </c>
-      <c r="B311" s="4" t="n">
+      <c r="B311" s="3" t="n">
         <v>45842</v>
       </c>
       <c r="C311" t="inlineStr">
@@ -14764,7 +14752,7 @@
           <t>ORD-00159</t>
         </is>
       </c>
-      <c r="B312" s="4" t="n">
+      <c r="B312" s="3" t="n">
         <v>45842</v>
       </c>
       <c r="C312" t="inlineStr">
@@ -14809,7 +14797,7 @@
           <t>ORD-00445</t>
         </is>
       </c>
-      <c r="B313" s="4" t="n">
+      <c r="B313" s="3" t="n">
         <v>45843</v>
       </c>
       <c r="C313" t="inlineStr">
@@ -14854,7 +14842,7 @@
           <t>ORD-00344</t>
         </is>
       </c>
-      <c r="B314" s="4" t="n">
+      <c r="B314" s="3" t="n">
         <v>45845</v>
       </c>
       <c r="C314" t="inlineStr">
@@ -14899,7 +14887,7 @@
           <t>ORD-00017</t>
         </is>
       </c>
-      <c r="B315" s="4" t="n">
+      <c r="B315" s="3" t="n">
         <v>45845</v>
       </c>
       <c r="C315" t="inlineStr">
@@ -14944,7 +14932,7 @@
           <t>ORD-00549</t>
         </is>
       </c>
-      <c r="B316" s="4" t="n">
+      <c r="B316" s="3" t="n">
         <v>45846</v>
       </c>
       <c r="C316" t="inlineStr">
@@ -14989,7 +14977,7 @@
           <t>ORD-00366</t>
         </is>
       </c>
-      <c r="B317" s="4" t="n">
+      <c r="B317" s="3" t="n">
         <v>45847</v>
       </c>
       <c r="C317" t="inlineStr">
@@ -15034,7 +15022,7 @@
           <t>ORD-00296</t>
         </is>
       </c>
-      <c r="B318" s="4" t="n">
+      <c r="B318" s="3" t="n">
         <v>45848</v>
       </c>
       <c r="C318" t="inlineStr">
@@ -15079,7 +15067,7 @@
           <t>ORD-00449</t>
         </is>
       </c>
-      <c r="B319" s="4" t="n">
+      <c r="B319" s="3" t="n">
         <v>45848</v>
       </c>
       <c r="C319" t="inlineStr">
@@ -15124,7 +15112,7 @@
           <t>ORD-00578</t>
         </is>
       </c>
-      <c r="B320" s="4" t="n">
+      <c r="B320" s="3" t="n">
         <v>45849</v>
       </c>
       <c r="C320" t="inlineStr">
@@ -15169,7 +15157,7 @@
           <t>ORD-00011</t>
         </is>
       </c>
-      <c r="B321" s="4" t="n">
+      <c r="B321" s="3" t="n">
         <v>45850</v>
       </c>
       <c r="C321" t="inlineStr">
@@ -15214,7 +15202,7 @@
           <t>ORD-00488</t>
         </is>
       </c>
-      <c r="B322" s="4" t="n">
+      <c r="B322" s="3" t="n">
         <v>45851</v>
       </c>
       <c r="C322" t="inlineStr">
@@ -15259,7 +15247,7 @@
           <t>ORD-00507</t>
         </is>
       </c>
-      <c r="B323" s="4" t="n">
+      <c r="B323" s="3" t="n">
         <v>45851</v>
       </c>
       <c r="C323" t="inlineStr">
@@ -15304,7 +15292,7 @@
           <t>ORD-00351</t>
         </is>
       </c>
-      <c r="B324" s="4" t="n">
+      <c r="B324" s="3" t="n">
         <v>45852</v>
       </c>
       <c r="C324" t="inlineStr">
@@ -15349,7 +15337,7 @@
           <t>ORD-00561</t>
         </is>
       </c>
-      <c r="B325" s="4" t="n">
+      <c r="B325" s="3" t="n">
         <v>45853</v>
       </c>
       <c r="C325" t="inlineStr">
@@ -15394,7 +15382,7 @@
           <t>ORD-00289</t>
         </is>
       </c>
-      <c r="B326" s="4" t="n">
+      <c r="B326" s="3" t="n">
         <v>45855</v>
       </c>
       <c r="C326" t="inlineStr">
@@ -15439,7 +15427,7 @@
           <t>ORD-00539</t>
         </is>
       </c>
-      <c r="B327" s="4" t="n">
+      <c r="B327" s="3" t="n">
         <v>45855</v>
       </c>
       <c r="C327" t="inlineStr">
@@ -15484,7 +15472,7 @@
           <t>ORD-00305</t>
         </is>
       </c>
-      <c r="B328" s="4" t="n">
+      <c r="B328" s="3" t="n">
         <v>45856</v>
       </c>
       <c r="C328" t="inlineStr">
@@ -15529,7 +15517,7 @@
           <t>ORD-00295</t>
         </is>
       </c>
-      <c r="B329" s="4" t="n">
+      <c r="B329" s="3" t="n">
         <v>45856</v>
       </c>
       <c r="C329" t="inlineStr">
@@ -15574,7 +15562,7 @@
           <t>ORD-00029</t>
         </is>
       </c>
-      <c r="B330" s="4" t="n">
+      <c r="B330" s="3" t="n">
         <v>45857</v>
       </c>
       <c r="C330" t="inlineStr">
@@ -15619,7 +15607,7 @@
           <t>ORD-00331</t>
         </is>
       </c>
-      <c r="B331" s="4" t="n">
+      <c r="B331" s="3" t="n">
         <v>45857</v>
       </c>
       <c r="C331" t="inlineStr">
@@ -15664,7 +15652,7 @@
           <t>ORD-00229</t>
         </is>
       </c>
-      <c r="B332" s="4" t="n">
+      <c r="B332" s="3" t="n">
         <v>45857</v>
       </c>
       <c r="C332" t="inlineStr">
@@ -15709,7 +15697,7 @@
           <t>ORD-00057</t>
         </is>
       </c>
-      <c r="B333" s="4" t="n">
+      <c r="B333" s="3" t="n">
         <v>45857</v>
       </c>
       <c r="C333" t="inlineStr">
@@ -15754,7 +15742,7 @@
           <t>ORD-00132</t>
         </is>
       </c>
-      <c r="B334" s="4" t="n">
+      <c r="B334" s="3" t="n">
         <v>45860</v>
       </c>
       <c r="C334" t="inlineStr">
@@ -15799,7 +15787,7 @@
           <t>ORD-00034</t>
         </is>
       </c>
-      <c r="B335" s="4" t="n">
+      <c r="B335" s="3" t="n">
         <v>45860</v>
       </c>
       <c r="C335" t="inlineStr">
@@ -15844,7 +15832,7 @@
           <t>ORD-00113</t>
         </is>
       </c>
-      <c r="B336" s="4" t="n">
+      <c r="B336" s="3" t="n">
         <v>45860</v>
       </c>
       <c r="C336" t="inlineStr">
@@ -15889,7 +15877,7 @@
           <t>ORD-00308</t>
         </is>
       </c>
-      <c r="B337" s="4" t="n">
+      <c r="B337" s="3" t="n">
         <v>45860</v>
       </c>
       <c r="C337" t="inlineStr">
@@ -15934,7 +15922,7 @@
           <t>ORD-00456</t>
         </is>
       </c>
-      <c r="B338" s="4" t="n">
+      <c r="B338" s="3" t="n">
         <v>45860</v>
       </c>
       <c r="C338" t="inlineStr">
@@ -15979,7 +15967,7 @@
           <t>ORD-00330</t>
         </is>
       </c>
-      <c r="B339" s="4" t="n">
+      <c r="B339" s="3" t="n">
         <v>45860</v>
       </c>
       <c r="C339" t="inlineStr">
@@ -16024,7 +16012,7 @@
           <t>ORD-00158</t>
         </is>
       </c>
-      <c r="B340" s="4" t="n">
+      <c r="B340" s="3" t="n">
         <v>45861</v>
       </c>
       <c r="C340" t="inlineStr">
@@ -16069,7 +16057,7 @@
           <t>ORD-00134</t>
         </is>
       </c>
-      <c r="B341" s="4" t="n">
+      <c r="B341" s="3" t="n">
         <v>45862</v>
       </c>
       <c r="C341" t="inlineStr">
@@ -16114,7 +16102,7 @@
           <t>ORD-00079</t>
         </is>
       </c>
-      <c r="B342" s="4" t="n">
+      <c r="B342" s="3" t="n">
         <v>45864</v>
       </c>
       <c r="C342" t="inlineStr">
@@ -16159,7 +16147,7 @@
           <t>ORD-00131</t>
         </is>
       </c>
-      <c r="B343" s="4" t="n">
+      <c r="B343" s="3" t="n">
         <v>45864</v>
       </c>
       <c r="C343" t="inlineStr">
@@ -16204,7 +16192,7 @@
           <t>ORD-00126</t>
         </is>
       </c>
-      <c r="B344" s="4" t="n">
+      <c r="B344" s="3" t="n">
         <v>45864</v>
       </c>
       <c r="C344" t="inlineStr">
@@ -16249,7 +16237,7 @@
           <t>ORD-00116</t>
         </is>
       </c>
-      <c r="B345" s="4" t="n">
+      <c r="B345" s="3" t="n">
         <v>45865</v>
       </c>
       <c r="C345" t="inlineStr">
@@ -16294,7 +16282,7 @@
           <t>ORD-00437</t>
         </is>
       </c>
-      <c r="B346" s="4" t="n">
+      <c r="B346" s="3" t="n">
         <v>45865</v>
       </c>
       <c r="C346" t="inlineStr">
@@ -16339,7 +16327,7 @@
           <t>ORD-00288</t>
         </is>
       </c>
-      <c r="B347" s="4" t="n">
+      <c r="B347" s="3" t="n">
         <v>45866</v>
       </c>
       <c r="C347" t="inlineStr">
@@ -16384,7 +16372,7 @@
           <t>ORD-00570</t>
         </is>
       </c>
-      <c r="B348" s="4" t="n">
+      <c r="B348" s="3" t="n">
         <v>45866</v>
       </c>
       <c r="C348" t="inlineStr">
@@ -16429,7 +16417,7 @@
           <t>ORD-00129</t>
         </is>
       </c>
-      <c r="B349" s="4" t="n">
+      <c r="B349" s="3" t="n">
         <v>45867</v>
       </c>
       <c r="C349" t="inlineStr">
@@ -16474,7 +16462,7 @@
           <t>ORD-00535</t>
         </is>
       </c>
-      <c r="B350" s="4" t="n">
+      <c r="B350" s="3" t="n">
         <v>45868</v>
       </c>
       <c r="C350" t="inlineStr">
@@ -16519,7 +16507,7 @@
           <t>ORD-00228</t>
         </is>
       </c>
-      <c r="B351" s="4" t="n">
+      <c r="B351" s="3" t="n">
         <v>45869</v>
       </c>
       <c r="C351" t="inlineStr">
@@ -16564,7 +16552,7 @@
           <t>ORD-00597</t>
         </is>
       </c>
-      <c r="B352" s="4" t="n">
+      <c r="B352" s="3" t="n">
         <v>45869</v>
       </c>
       <c r="C352" t="inlineStr">
@@ -16609,7 +16597,7 @@
           <t>ORD-00266</t>
         </is>
       </c>
-      <c r="B353" s="4" t="n">
+      <c r="B353" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="C353" t="inlineStr">
@@ -16654,7 +16642,7 @@
           <t>ORD-00424</t>
         </is>
       </c>
-      <c r="B354" s="4" t="n">
+      <c r="B354" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="C354" t="inlineStr">
@@ -16699,7 +16687,7 @@
           <t>ORD-00242</t>
         </is>
       </c>
-      <c r="B355" s="4" t="n">
+      <c r="B355" s="3" t="n">
         <v>45871</v>
       </c>
       <c r="C355" t="inlineStr">
@@ -16744,7 +16732,7 @@
           <t>ORD-00260</t>
         </is>
       </c>
-      <c r="B356" s="4" t="n">
+      <c r="B356" s="3" t="n">
         <v>45872</v>
       </c>
       <c r="C356" t="inlineStr">
@@ -16789,7 +16777,7 @@
           <t>ORD-00270</t>
         </is>
       </c>
-      <c r="B357" s="4" t="n">
+      <c r="B357" s="3" t="n">
         <v>45873</v>
       </c>
       <c r="C357" t="inlineStr">
@@ -16834,7 +16822,7 @@
           <t>ORD-00548</t>
         </is>
       </c>
-      <c r="B358" s="4" t="n">
+      <c r="B358" s="3" t="n">
         <v>45873</v>
       </c>
       <c r="C358" t="inlineStr">
@@ -16879,7 +16867,7 @@
           <t>ORD-00520</t>
         </is>
       </c>
-      <c r="B359" s="4" t="n">
+      <c r="B359" s="3" t="n">
         <v>45874</v>
       </c>
       <c r="C359" t="inlineStr">
@@ -16924,7 +16912,7 @@
           <t>ORD-00455</t>
         </is>
       </c>
-      <c r="B360" s="4" t="n">
+      <c r="B360" s="3" t="n">
         <v>45875</v>
       </c>
       <c r="C360" t="inlineStr">
@@ -16969,7 +16957,7 @@
           <t>ORD-00468</t>
         </is>
       </c>
-      <c r="B361" s="4" t="n">
+      <c r="B361" s="3" t="n">
         <v>45875</v>
       </c>
       <c r="C361" t="inlineStr">
@@ -17014,7 +17002,7 @@
           <t>ORD-00394</t>
         </is>
       </c>
-      <c r="B362" s="4" t="n">
+      <c r="B362" s="3" t="n">
         <v>45876</v>
       </c>
       <c r="C362" t="inlineStr">
@@ -17059,7 +17047,7 @@
           <t>ORD-00531</t>
         </is>
       </c>
-      <c r="B363" s="4" t="n">
+      <c r="B363" s="3" t="n">
         <v>45876</v>
       </c>
       <c r="C363" t="inlineStr">
@@ -17104,7 +17092,7 @@
           <t>ORD-00137</t>
         </is>
       </c>
-      <c r="B364" s="4" t="n">
+      <c r="B364" s="3" t="n">
         <v>45878</v>
       </c>
       <c r="C364" t="inlineStr">
@@ -17149,7 +17137,7 @@
           <t>ORD-00494</t>
         </is>
       </c>
-      <c r="B365" s="4" t="n">
+      <c r="B365" s="3" t="n">
         <v>45878</v>
       </c>
       <c r="C365" t="inlineStr">
@@ -17194,7 +17182,7 @@
           <t>ORD-00193</t>
         </is>
       </c>
-      <c r="B366" s="4" t="n">
+      <c r="B366" s="3" t="n">
         <v>45879</v>
       </c>
       <c r="C366" t="inlineStr">
@@ -17239,7 +17227,7 @@
           <t>ORD-00490</t>
         </is>
       </c>
-      <c r="B367" s="4" t="n">
+      <c r="B367" s="3" t="n">
         <v>45879</v>
       </c>
       <c r="C367" t="inlineStr">
@@ -17284,7 +17272,7 @@
           <t>ORD-00269</t>
         </is>
       </c>
-      <c r="B368" s="4" t="n">
+      <c r="B368" s="3" t="n">
         <v>45881</v>
       </c>
       <c r="C368" t="inlineStr">
@@ -17329,7 +17317,7 @@
           <t>ORD-00323</t>
         </is>
       </c>
-      <c r="B369" s="4" t="n">
+      <c r="B369" s="3" t="n">
         <v>45882</v>
       </c>
       <c r="C369" t="inlineStr">
@@ -17374,7 +17362,7 @@
           <t>ORD-00343</t>
         </is>
       </c>
-      <c r="B370" s="4" t="n">
+      <c r="B370" s="3" t="n">
         <v>45884</v>
       </c>
       <c r="C370" t="inlineStr">
@@ -17419,7 +17407,7 @@
           <t>ORD-00240</t>
         </is>
       </c>
-      <c r="B371" s="4" t="n">
+      <c r="B371" s="3" t="n">
         <v>45886</v>
       </c>
       <c r="C371" t="inlineStr">
@@ -17464,7 +17452,7 @@
           <t>ORD-00245</t>
         </is>
       </c>
-      <c r="B372" s="4" t="n">
+      <c r="B372" s="3" t="n">
         <v>45887</v>
       </c>
       <c r="C372" t="inlineStr">
@@ -17509,7 +17497,7 @@
           <t>ORD-00085</t>
         </is>
       </c>
-      <c r="B373" s="4" t="n">
+      <c r="B373" s="3" t="n">
         <v>45887</v>
       </c>
       <c r="C373" t="inlineStr">
@@ -17554,7 +17542,7 @@
           <t>ORD-00599</t>
         </is>
       </c>
-      <c r="B374" s="4" t="n">
+      <c r="B374" s="3" t="n">
         <v>45887</v>
       </c>
       <c r="C374" t="inlineStr">
@@ -17599,7 +17587,7 @@
           <t>ORD-00192</t>
         </is>
       </c>
-      <c r="B375" s="4" t="n">
+      <c r="B375" s="3" t="n">
         <v>45888</v>
       </c>
       <c r="C375" t="inlineStr">
@@ -17644,7 +17632,7 @@
           <t>ORD-00040</t>
         </is>
       </c>
-      <c r="B376" s="4" t="n">
+      <c r="B376" s="3" t="n">
         <v>45888</v>
       </c>
       <c r="C376" t="inlineStr">
@@ -17689,7 +17677,7 @@
           <t>ORD-00458</t>
         </is>
       </c>
-      <c r="B377" s="4" t="n">
+      <c r="B377" s="3" t="n">
         <v>45889</v>
       </c>
       <c r="C377" t="inlineStr">
@@ -17734,7 +17722,7 @@
           <t>ORD-00130</t>
         </is>
       </c>
-      <c r="B378" s="4" t="n">
+      <c r="B378" s="3" t="n">
         <v>45889</v>
       </c>
       <c r="C378" t="inlineStr">
@@ -17779,7 +17767,7 @@
           <t>ORD-00475</t>
         </is>
       </c>
-      <c r="B379" s="4" t="n">
+      <c r="B379" s="3" t="n">
         <v>45889</v>
       </c>
       <c r="C379" t="inlineStr">
@@ -17824,7 +17812,7 @@
           <t>ORD-00341</t>
         </is>
       </c>
-      <c r="B380" s="4" t="n">
+      <c r="B380" s="3" t="n">
         <v>45889</v>
       </c>
       <c r="C380" t="inlineStr">
@@ -17869,7 +17857,7 @@
           <t>ORD-00099</t>
         </is>
       </c>
-      <c r="B381" s="4" t="n">
+      <c r="B381" s="3" t="n">
         <v>45890</v>
       </c>
       <c r="C381" t="inlineStr">
@@ -17914,7 +17902,7 @@
           <t>ORD-00600</t>
         </is>
       </c>
-      <c r="B382" s="4" t="n">
+      <c r="B382" s="3" t="n">
         <v>45892</v>
       </c>
       <c r="C382" t="inlineStr">
@@ -17959,7 +17947,7 @@
           <t>ORD-00569</t>
         </is>
       </c>
-      <c r="B383" s="4" t="n">
+      <c r="B383" s="3" t="n">
         <v>45892</v>
       </c>
       <c r="C383" t="inlineStr">
@@ -18004,7 +17992,7 @@
           <t>ORD-00026</t>
         </is>
       </c>
-      <c r="B384" s="4" t="n">
+      <c r="B384" s="3" t="n">
         <v>45893</v>
       </c>
       <c r="C384" t="inlineStr">
@@ -18049,7 +18037,7 @@
           <t>ORD-00502</t>
         </is>
       </c>
-      <c r="B385" s="4" t="n">
+      <c r="B385" s="3" t="n">
         <v>45895</v>
       </c>
       <c r="C385" t="inlineStr">
@@ -18094,7 +18082,7 @@
           <t>ORD-00244</t>
         </is>
       </c>
-      <c r="B386" s="4" t="n">
+      <c r="B386" s="3" t="n">
         <v>45895</v>
       </c>
       <c r="C386" t="inlineStr">
@@ -18139,7 +18127,7 @@
           <t>ORD-00123</t>
         </is>
       </c>
-      <c r="B387" s="4" t="n">
+      <c r="B387" s="3" t="n">
         <v>45896</v>
       </c>
       <c r="C387" t="inlineStr">
@@ -18184,7 +18172,7 @@
           <t>ORD-00003</t>
         </is>
       </c>
-      <c r="B388" s="4" t="n">
+      <c r="B388" s="3" t="n">
         <v>45896</v>
       </c>
       <c r="C388" t="inlineStr">
@@ -18229,7 +18217,7 @@
           <t>ORD-00316</t>
         </is>
       </c>
-      <c r="B389" s="4" t="n">
+      <c r="B389" s="3" t="n">
         <v>45898</v>
       </c>
       <c r="C389" t="inlineStr">
@@ -18274,7 +18262,7 @@
           <t>ORD-00255</t>
         </is>
       </c>
-      <c r="B390" s="4" t="n">
+      <c r="B390" s="3" t="n">
         <v>45899</v>
       </c>
       <c r="C390" t="inlineStr">
@@ -18319,7 +18307,7 @@
           <t>ORD-00372</t>
         </is>
       </c>
-      <c r="B391" s="4" t="n">
+      <c r="B391" s="3" t="n">
         <v>45899</v>
       </c>
       <c r="C391" t="inlineStr">
@@ -18364,7 +18352,7 @@
           <t>ORD-00446</t>
         </is>
       </c>
-      <c r="B392" s="4" t="n">
+      <c r="B392" s="3" t="n">
         <v>45899</v>
       </c>
       <c r="C392" t="inlineStr">
@@ -18409,7 +18397,7 @@
           <t>ORD-00156</t>
         </is>
       </c>
-      <c r="B393" s="4" t="n">
+      <c r="B393" s="3" t="n">
         <v>45899</v>
       </c>
       <c r="C393" t="inlineStr">
@@ -18454,7 +18442,7 @@
           <t>ORD-00237</t>
         </is>
       </c>
-      <c r="B394" s="4" t="n">
+      <c r="B394" s="3" t="n">
         <v>45900</v>
       </c>
       <c r="C394" t="inlineStr">
@@ -18499,7 +18487,7 @@
           <t>ORD-00108</t>
         </is>
       </c>
-      <c r="B395" s="4" t="n">
+      <c r="B395" s="3" t="n">
         <v>45900</v>
       </c>
       <c r="C395" t="inlineStr">
@@ -18544,7 +18532,7 @@
           <t>ORD-00162</t>
         </is>
       </c>
-      <c r="B396" s="4" t="n">
+      <c r="B396" s="3" t="n">
         <v>45900</v>
       </c>
       <c r="C396" t="inlineStr">
@@ -18589,7 +18577,7 @@
           <t>ORD-00479</t>
         </is>
       </c>
-      <c r="B397" s="4" t="n">
+      <c r="B397" s="3" t="n">
         <v>45900</v>
       </c>
       <c r="C397" t="inlineStr">
@@ -18634,7 +18622,7 @@
           <t>ORD-00122</t>
         </is>
       </c>
-      <c r="B398" s="4" t="n">
+      <c r="B398" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="C398" t="inlineStr">
@@ -18679,7 +18667,7 @@
           <t>ORD-00311</t>
         </is>
       </c>
-      <c r="B399" s="4" t="n">
+      <c r="B399" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="C399" t="inlineStr">
@@ -18724,7 +18712,7 @@
           <t>ORD-00283</t>
         </is>
       </c>
-      <c r="B400" s="4" t="n">
+      <c r="B400" s="3" t="n">
         <v>45902</v>
       </c>
       <c r="C400" t="inlineStr">
@@ -18769,7 +18757,7 @@
           <t>ORD-00080</t>
         </is>
       </c>
-      <c r="B401" s="4" t="n">
+      <c r="B401" s="3" t="n">
         <v>45902</v>
       </c>
       <c r="C401" t="inlineStr">
@@ -18814,7 +18802,7 @@
           <t>ORD-00312</t>
         </is>
       </c>
-      <c r="B402" s="4" t="n">
+      <c r="B402" s="3" t="n">
         <v>45903</v>
       </c>
       <c r="C402" t="inlineStr">
@@ -18859,7 +18847,7 @@
           <t>ORD-00049</t>
         </is>
       </c>
-      <c r="B403" s="4" t="n">
+      <c r="B403" s="3" t="n">
         <v>45905</v>
       </c>
       <c r="C403" t="inlineStr">
@@ -18904,7 +18892,7 @@
           <t>ORD-00416</t>
         </is>
       </c>
-      <c r="B404" s="4" t="n">
+      <c r="B404" s="3" t="n">
         <v>45905</v>
       </c>
       <c r="C404" t="inlineStr">
@@ -18949,7 +18937,7 @@
           <t>ORD-00257</t>
         </is>
       </c>
-      <c r="B405" s="4" t="n">
+      <c r="B405" s="3" t="n">
         <v>45905</v>
       </c>
       <c r="C405" t="inlineStr">
@@ -18994,7 +18982,7 @@
           <t>ORD-00550</t>
         </is>
       </c>
-      <c r="B406" s="4" t="n">
+      <c r="B406" s="3" t="n">
         <v>45906</v>
       </c>
       <c r="C406" t="inlineStr">
@@ -19039,7 +19027,7 @@
           <t>ORD-00060</t>
         </is>
       </c>
-      <c r="B407" s="4" t="n">
+      <c r="B407" s="3" t="n">
         <v>45907</v>
       </c>
       <c r="C407" t="inlineStr">
@@ -19084,7 +19072,7 @@
           <t>ORD-00098</t>
         </is>
       </c>
-      <c r="B408" s="4" t="n">
+      <c r="B408" s="3" t="n">
         <v>45907</v>
       </c>
       <c r="C408" t="inlineStr">
@@ -19129,7 +19117,7 @@
           <t>ORD-00191</t>
         </is>
       </c>
-      <c r="B409" s="4" t="n">
+      <c r="B409" s="3" t="n">
         <v>45907</v>
       </c>
       <c r="C409" t="inlineStr">
@@ -19174,7 +19162,7 @@
           <t>ORD-00075</t>
         </is>
       </c>
-      <c r="B410" s="4" t="n">
+      <c r="B410" s="3" t="n">
         <v>45908</v>
       </c>
       <c r="C410" t="inlineStr">
@@ -19219,7 +19207,7 @@
           <t>ORD-00587</t>
         </is>
       </c>
-      <c r="B411" s="4" t="n">
+      <c r="B411" s="3" t="n">
         <v>45909</v>
       </c>
       <c r="C411" t="inlineStr">
@@ -19264,7 +19252,7 @@
           <t>ORD-00422</t>
         </is>
       </c>
-      <c r="B412" s="4" t="n">
+      <c r="B412" s="3" t="n">
         <v>45911</v>
       </c>
       <c r="C412" t="inlineStr">
@@ -19309,7 +19297,7 @@
           <t>ORD-00184</t>
         </is>
       </c>
-      <c r="B413" s="4" t="n">
+      <c r="B413" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="C413" t="inlineStr">
@@ -19354,7 +19342,7 @@
           <t>ORD-00008</t>
         </is>
       </c>
-      <c r="B414" s="4" t="n">
+      <c r="B414" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="C414" t="inlineStr">
@@ -19399,7 +19387,7 @@
           <t>ORD-00175</t>
         </is>
       </c>
-      <c r="B415" s="4" t="n">
+      <c r="B415" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="C415" t="inlineStr">
@@ -19444,7 +19432,7 @@
           <t>ORD-00204</t>
         </is>
       </c>
-      <c r="B416" s="4" t="n">
+      <c r="B416" s="3" t="n">
         <v>45913</v>
       </c>
       <c r="C416" t="inlineStr">
@@ -19489,7 +19477,7 @@
           <t>ORD-00086</t>
         </is>
       </c>
-      <c r="B417" s="4" t="n">
+      <c r="B417" s="3" t="n">
         <v>45913</v>
       </c>
       <c r="C417" t="inlineStr">
@@ -19534,7 +19522,7 @@
           <t>ORD-00043</t>
         </is>
       </c>
-      <c r="B418" s="4" t="n">
+      <c r="B418" s="3" t="n">
         <v>45913</v>
       </c>
       <c r="C418" t="inlineStr">
@@ -19579,7 +19567,7 @@
           <t>ORD-00223</t>
         </is>
       </c>
-      <c r="B419" s="4" t="n">
+      <c r="B419" s="3" t="n">
         <v>45914</v>
       </c>
       <c r="C419" t="inlineStr">
@@ -19624,7 +19612,7 @@
           <t>ORD-00110</t>
         </is>
       </c>
-      <c r="B420" s="4" t="n">
+      <c r="B420" s="3" t="n">
         <v>45915</v>
       </c>
       <c r="C420" t="inlineStr">
@@ -19669,7 +19657,7 @@
           <t>ORD-00541</t>
         </is>
       </c>
-      <c r="B421" s="4" t="n">
+      <c r="B421" s="3" t="n">
         <v>45916</v>
       </c>
       <c r="C421" t="inlineStr">
@@ -19714,7 +19702,7 @@
           <t>ORD-00015</t>
         </is>
       </c>
-      <c r="B422" s="4" t="n">
+      <c r="B422" s="3" t="n">
         <v>45919</v>
       </c>
       <c r="C422" t="inlineStr">
@@ -19759,7 +19747,7 @@
           <t>ORD-00212</t>
         </is>
       </c>
-      <c r="B423" s="4" t="n">
+      <c r="B423" s="3" t="n">
         <v>45919</v>
       </c>
       <c r="C423" t="inlineStr">
@@ -19804,7 +19792,7 @@
           <t>ORD-00177</t>
         </is>
       </c>
-      <c r="B424" s="4" t="n">
+      <c r="B424" s="3" t="n">
         <v>45919</v>
       </c>
       <c r="C424" t="inlineStr">
@@ -19849,7 +19837,7 @@
           <t>ORD-00430</t>
         </is>
       </c>
-      <c r="B425" s="4" t="n">
+      <c r="B425" s="3" t="n">
         <v>45919</v>
       </c>
       <c r="C425" t="inlineStr">
@@ -19894,7 +19882,7 @@
           <t>ORD-00395</t>
         </is>
       </c>
-      <c r="B426" s="4" t="n">
+      <c r="B426" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="C426" t="inlineStr">
@@ -19939,7 +19927,7 @@
           <t>ORD-00236</t>
         </is>
       </c>
-      <c r="B427" s="4" t="n">
+      <c r="B427" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="C427" t="inlineStr">
@@ -19984,7 +19972,7 @@
           <t>ORD-00174</t>
         </is>
       </c>
-      <c r="B428" s="4" t="n">
+      <c r="B428" s="3" t="n">
         <v>45921</v>
       </c>
       <c r="C428" t="inlineStr">
@@ -20029,7 +20017,7 @@
           <t>ORD-00225</t>
         </is>
       </c>
-      <c r="B429" s="4" t="n">
+      <c r="B429" s="3" t="n">
         <v>45921</v>
       </c>
       <c r="C429" t="inlineStr">
@@ -20074,7 +20062,7 @@
           <t>ORD-00461</t>
         </is>
       </c>
-      <c r="B430" s="4" t="n">
+      <c r="B430" s="3" t="n">
         <v>45922</v>
       </c>
       <c r="C430" t="inlineStr">
@@ -20119,7 +20107,7 @@
           <t>ORD-00318</t>
         </is>
       </c>
-      <c r="B431" s="4" t="n">
+      <c r="B431" s="3" t="n">
         <v>45923</v>
       </c>
       <c r="C431" t="inlineStr">
@@ -20164,7 +20152,7 @@
           <t>ORD-00317</t>
         </is>
       </c>
-      <c r="B432" s="4" t="n">
+      <c r="B432" s="3" t="n">
         <v>45924</v>
       </c>
       <c r="C432" t="inlineStr">
@@ -20209,7 +20197,7 @@
           <t>ORD-00377</t>
         </is>
       </c>
-      <c r="B433" s="4" t="n">
+      <c r="B433" s="3" t="n">
         <v>45926</v>
       </c>
       <c r="C433" t="inlineStr">
@@ -20254,7 +20242,7 @@
           <t>ORD-00013</t>
         </is>
       </c>
-      <c r="B434" s="4" t="n">
+      <c r="B434" s="3" t="n">
         <v>45926</v>
       </c>
       <c r="C434" t="inlineStr">
@@ -20299,7 +20287,7 @@
           <t>ORD-00215</t>
         </is>
       </c>
-      <c r="B435" s="4" t="n">
+      <c r="B435" s="3" t="n">
         <v>45926</v>
       </c>
       <c r="C435" t="inlineStr">
@@ -20344,7 +20332,7 @@
           <t>ORD-00557</t>
         </is>
       </c>
-      <c r="B436" s="4" t="n">
+      <c r="B436" s="3" t="n">
         <v>45926</v>
       </c>
       <c r="C436" t="inlineStr">
@@ -20389,7 +20377,7 @@
           <t>ORD-00471</t>
         </is>
       </c>
-      <c r="B437" s="4" t="n">
+      <c r="B437" s="3" t="n">
         <v>45927</v>
       </c>
       <c r="C437" t="inlineStr">
@@ -20434,7 +20422,7 @@
           <t>ORD-00432</t>
         </is>
       </c>
-      <c r="B438" s="4" t="n">
+      <c r="B438" s="3" t="n">
         <v>45927</v>
       </c>
       <c r="C438" t="inlineStr">
@@ -20479,7 +20467,7 @@
           <t>ORD-00059</t>
         </is>
       </c>
-      <c r="B439" s="4" t="n">
+      <c r="B439" s="3" t="n">
         <v>45929</v>
       </c>
       <c r="C439" t="inlineStr">
@@ -20524,7 +20512,7 @@
           <t>ORD-00062</t>
         </is>
       </c>
-      <c r="B440" s="4" t="n">
+      <c r="B440" s="3" t="n">
         <v>45929</v>
       </c>
       <c r="C440" t="inlineStr">
@@ -20569,7 +20557,7 @@
           <t>ORD-00512</t>
         </is>
       </c>
-      <c r="B441" s="4" t="n">
+      <c r="B441" s="3" t="n">
         <v>45930</v>
       </c>
       <c r="C441" t="inlineStr">
@@ -20614,7 +20602,7 @@
           <t>ORD-00378</t>
         </is>
       </c>
-      <c r="B442" s="4" t="n">
+      <c r="B442" s="3" t="n">
         <v>45930</v>
       </c>
       <c r="C442" t="inlineStr">
@@ -20659,7 +20647,7 @@
           <t>ORD-00391</t>
         </is>
       </c>
-      <c r="B443" s="4" t="n">
+      <c r="B443" s="3" t="n">
         <v>45930</v>
       </c>
       <c r="C443" t="inlineStr">
@@ -20704,7 +20692,7 @@
           <t>ORD-00360</t>
         </is>
       </c>
-      <c r="B444" s="4" t="n">
+      <c r="B444" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="C444" t="inlineStr">
@@ -20749,7 +20737,7 @@
           <t>ORD-00463</t>
         </is>
       </c>
-      <c r="B445" s="4" t="n">
+      <c r="B445" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="C445" t="inlineStr">
@@ -20794,7 +20782,7 @@
           <t>ORD-00493</t>
         </is>
       </c>
-      <c r="B446" s="4" t="n">
+      <c r="B446" s="3" t="n">
         <v>45932</v>
       </c>
       <c r="C446" t="inlineStr">
@@ -20839,7 +20827,7 @@
           <t>ORD-00234</t>
         </is>
       </c>
-      <c r="B447" s="4" t="n">
+      <c r="B447" s="3" t="n">
         <v>45934</v>
       </c>
       <c r="C447" t="inlineStr">
@@ -20884,7 +20872,7 @@
           <t>ORD-00042</t>
         </is>
       </c>
-      <c r="B448" s="4" t="n">
+      <c r="B448" s="3" t="n">
         <v>45934</v>
       </c>
       <c r="C448" t="inlineStr">
@@ -20929,7 +20917,7 @@
           <t>ORD-00247</t>
         </is>
       </c>
-      <c r="B449" s="4" t="n">
+      <c r="B449" s="3" t="n">
         <v>45934</v>
       </c>
       <c r="C449" t="inlineStr">
@@ -20974,7 +20962,7 @@
           <t>ORD-00051</t>
         </is>
       </c>
-      <c r="B450" s="4" t="n">
+      <c r="B450" s="3" t="n">
         <v>45935</v>
       </c>
       <c r="C450" t="inlineStr">
@@ -21019,7 +21007,7 @@
           <t>ORD-00014</t>
         </is>
       </c>
-      <c r="B451" s="4" t="n">
+      <c r="B451" s="3" t="n">
         <v>45935</v>
       </c>
       <c r="C451" t="inlineStr">
@@ -21064,7 +21052,7 @@
           <t>ORD-00207</t>
         </is>
       </c>
-      <c r="B452" s="4" t="n">
+      <c r="B452" s="3" t="n">
         <v>45936</v>
       </c>
       <c r="C452" t="inlineStr">
@@ -21109,7 +21097,7 @@
           <t>ORD-00128</t>
         </is>
       </c>
-      <c r="B453" s="4" t="n">
+      <c r="B453" s="3" t="n">
         <v>45937</v>
       </c>
       <c r="C453" t="inlineStr">
@@ -21154,7 +21142,7 @@
           <t>ORD-00489</t>
         </is>
       </c>
-      <c r="B454" s="4" t="n">
+      <c r="B454" s="3" t="n">
         <v>45937</v>
       </c>
       <c r="C454" t="inlineStr">
@@ -21199,7 +21187,7 @@
           <t>ORD-00423</t>
         </is>
       </c>
-      <c r="B455" s="4" t="n">
+      <c r="B455" s="3" t="n">
         <v>45937</v>
       </c>
       <c r="C455" t="inlineStr">
@@ -21244,7 +21232,7 @@
           <t>ORD-00089</t>
         </is>
       </c>
-      <c r="B456" s="4" t="n">
+      <c r="B456" s="3" t="n">
         <v>45938</v>
       </c>
       <c r="C456" t="inlineStr">
@@ -21289,7 +21277,7 @@
           <t>ORD-00320</t>
         </is>
       </c>
-      <c r="B457" s="4" t="n">
+      <c r="B457" s="3" t="n">
         <v>45938</v>
       </c>
       <c r="C457" t="inlineStr">
@@ -21334,7 +21322,7 @@
           <t>ORD-00370</t>
         </is>
       </c>
-      <c r="B458" s="4" t="n">
+      <c r="B458" s="3" t="n">
         <v>45939</v>
       </c>
       <c r="C458" t="inlineStr">
@@ -21379,7 +21367,7 @@
           <t>ORD-00173</t>
         </is>
       </c>
-      <c r="B459" s="4" t="n">
+      <c r="B459" s="3" t="n">
         <v>45939</v>
       </c>
       <c r="C459" t="inlineStr">
@@ -21424,7 +21412,7 @@
           <t>ORD-00002</t>
         </is>
       </c>
-      <c r="B460" s="4" t="n">
+      <c r="B460" s="3" t="n">
         <v>45940</v>
       </c>
       <c r="C460" t="inlineStr">
@@ -21469,7 +21457,7 @@
           <t>ORD-00402</t>
         </is>
       </c>
-      <c r="B461" s="4" t="n">
+      <c r="B461" s="3" t="n">
         <v>45941</v>
       </c>
       <c r="C461" t="inlineStr">
@@ -21514,7 +21502,7 @@
           <t>ORD-00112</t>
         </is>
       </c>
-      <c r="B462" s="4" t="n">
+      <c r="B462" s="3" t="n">
         <v>45942</v>
       </c>
       <c r="C462" t="inlineStr">
@@ -21559,7 +21547,7 @@
           <t>ORD-00107</t>
         </is>
       </c>
-      <c r="B463" s="4" t="n">
+      <c r="B463" s="3" t="n">
         <v>45942</v>
       </c>
       <c r="C463" t="inlineStr">
@@ -21604,7 +21592,7 @@
           <t>ORD-00210</t>
         </is>
       </c>
-      <c r="B464" s="4" t="n">
+      <c r="B464" s="3" t="n">
         <v>45942</v>
       </c>
       <c r="C464" t="inlineStr">
@@ -21649,7 +21637,7 @@
           <t>ORD-00598</t>
         </is>
       </c>
-      <c r="B465" s="4" t="n">
+      <c r="B465" s="3" t="n">
         <v>45942</v>
       </c>
       <c r="C465" t="inlineStr">
@@ -21694,7 +21682,7 @@
           <t>ORD-00050</t>
         </is>
       </c>
-      <c r="B466" s="4" t="n">
+      <c r="B466" s="3" t="n">
         <v>45942</v>
       </c>
       <c r="C466" t="inlineStr">
@@ -21739,7 +21727,7 @@
           <t>ORD-00025</t>
         </is>
       </c>
-      <c r="B467" s="4" t="n">
+      <c r="B467" s="3" t="n">
         <v>45943</v>
       </c>
       <c r="C467" t="inlineStr">
@@ -21784,7 +21772,7 @@
           <t>ORD-00278</t>
         </is>
       </c>
-      <c r="B468" s="4" t="n">
+      <c r="B468" s="3" t="n">
         <v>45943</v>
       </c>
       <c r="C468" t="inlineStr">
@@ -21829,7 +21817,7 @@
           <t>ORD-00476</t>
         </is>
       </c>
-      <c r="B469" s="4" t="n">
+      <c r="B469" s="3" t="n">
         <v>45944</v>
       </c>
       <c r="C469" t="inlineStr">
@@ -21874,7 +21862,7 @@
           <t>ORD-00016</t>
         </is>
       </c>
-      <c r="B470" s="4" t="n">
+      <c r="B470" s="3" t="n">
         <v>45944</v>
       </c>
       <c r="C470" t="inlineStr">
@@ -21919,7 +21907,7 @@
           <t>ORD-00160</t>
         </is>
       </c>
-      <c r="B471" s="4" t="n">
+      <c r="B471" s="3" t="n">
         <v>45944</v>
       </c>
       <c r="C471" t="inlineStr">
@@ -21964,7 +21952,7 @@
           <t>ORD-00249</t>
         </is>
       </c>
-      <c r="B472" s="4" t="n">
+      <c r="B472" s="3" t="n">
         <v>45945</v>
       </c>
       <c r="C472" t="inlineStr">
@@ -22009,7 +21997,7 @@
           <t>ORD-00106</t>
         </is>
       </c>
-      <c r="B473" s="4" t="n">
+      <c r="B473" s="3" t="n">
         <v>45945</v>
       </c>
       <c r="C473" t="inlineStr">
@@ -22054,7 +22042,7 @@
           <t>ORD-00213</t>
         </is>
       </c>
-      <c r="B474" s="4" t="n">
+      <c r="B474" s="3" t="n">
         <v>45945</v>
       </c>
       <c r="C474" t="inlineStr">
@@ -22099,7 +22087,7 @@
           <t>ORD-00559</t>
         </is>
       </c>
-      <c r="B475" s="4" t="n">
+      <c r="B475" s="3" t="n">
         <v>45947</v>
       </c>
       <c r="C475" t="inlineStr">
@@ -22144,7 +22132,7 @@
           <t>ORD-00261</t>
         </is>
       </c>
-      <c r="B476" s="4" t="n">
+      <c r="B476" s="3" t="n">
         <v>45947</v>
       </c>
       <c r="C476" t="inlineStr">
@@ -22189,7 +22177,7 @@
           <t>ORD-00135</t>
         </is>
       </c>
-      <c r="B477" s="4" t="n">
+      <c r="B477" s="3" t="n">
         <v>45948</v>
       </c>
       <c r="C477" t="inlineStr">
@@ -22234,7 +22222,7 @@
           <t>ORD-00484</t>
         </is>
       </c>
-      <c r="B478" s="4" t="n">
+      <c r="B478" s="3" t="n">
         <v>45948</v>
       </c>
       <c r="C478" t="inlineStr">
@@ -22279,7 +22267,7 @@
           <t>ORD-00071</t>
         </is>
       </c>
-      <c r="B479" s="4" t="n">
+      <c r="B479" s="3" t="n">
         <v>45948</v>
       </c>
       <c r="C479" t="inlineStr">
@@ -22324,7 +22312,7 @@
           <t>ORD-00105</t>
         </is>
       </c>
-      <c r="B480" s="4" t="n">
+      <c r="B480" s="3" t="n">
         <v>45948</v>
       </c>
       <c r="C480" t="inlineStr">
@@ -22369,7 +22357,7 @@
           <t>ORD-00591</t>
         </is>
       </c>
-      <c r="B481" s="4" t="n">
+      <c r="B481" s="3" t="n">
         <v>45950</v>
       </c>
       <c r="C481" t="inlineStr">
@@ -22414,7 +22402,7 @@
           <t>ORD-00596</t>
         </is>
       </c>
-      <c r="B482" s="4" t="n">
+      <c r="B482" s="3" t="n">
         <v>45950</v>
       </c>
       <c r="C482" t="inlineStr">
@@ -22459,7 +22447,7 @@
           <t>ORD-00428</t>
         </is>
       </c>
-      <c r="B483" s="4" t="n">
+      <c r="B483" s="3" t="n">
         <v>45951</v>
       </c>
       <c r="C483" t="inlineStr">
@@ -22504,7 +22492,7 @@
           <t>ORD-00092</t>
         </is>
       </c>
-      <c r="B484" s="4" t="n">
+      <c r="B484" s="3" t="n">
         <v>45951</v>
       </c>
       <c r="C484" t="inlineStr">
@@ -22549,7 +22537,7 @@
           <t>ORD-00551</t>
         </is>
       </c>
-      <c r="B485" s="4" t="n">
+      <c r="B485" s="3" t="n">
         <v>45951</v>
       </c>
       <c r="C485" t="inlineStr">
@@ -22594,7 +22582,7 @@
           <t>ORD-00472</t>
         </is>
       </c>
-      <c r="B486" s="4" t="n">
+      <c r="B486" s="3" t="n">
         <v>45951</v>
       </c>
       <c r="C486" t="inlineStr">
@@ -22639,7 +22627,7 @@
           <t>ORD-00103</t>
         </is>
       </c>
-      <c r="B487" s="4" t="n">
+      <c r="B487" s="3" t="n">
         <v>45951</v>
       </c>
       <c r="C487" t="inlineStr">
@@ -22684,7 +22672,7 @@
           <t>ORD-00291</t>
         </is>
       </c>
-      <c r="B488" s="4" t="n">
+      <c r="B488" s="3" t="n">
         <v>45952</v>
       </c>
       <c r="C488" t="inlineStr">
@@ -22729,7 +22717,7 @@
           <t>ORD-00227</t>
         </is>
       </c>
-      <c r="B489" s="4" t="n">
+      <c r="B489" s="3" t="n">
         <v>45953</v>
       </c>
       <c r="C489" t="inlineStr">
@@ -22774,7 +22762,7 @@
           <t>ORD-00336</t>
         </is>
       </c>
-      <c r="B490" s="4" t="n">
+      <c r="B490" s="3" t="n">
         <v>45953</v>
       </c>
       <c r="C490" t="inlineStr">
@@ -22819,7 +22807,7 @@
           <t>ORD-00166</t>
         </is>
       </c>
-      <c r="B491" s="4" t="n">
+      <c r="B491" s="3" t="n">
         <v>45955</v>
       </c>
       <c r="C491" t="inlineStr">
@@ -22864,7 +22852,7 @@
           <t>ORD-00514</t>
         </is>
       </c>
-      <c r="B492" s="4" t="n">
+      <c r="B492" s="3" t="n">
         <v>45956</v>
       </c>
       <c r="C492" t="inlineStr">
@@ -22909,7 +22897,7 @@
           <t>ORD-00149</t>
         </is>
       </c>
-      <c r="B493" s="4" t="n">
+      <c r="B493" s="3" t="n">
         <v>45957</v>
       </c>
       <c r="C493" t="inlineStr">
@@ -22954,7 +22942,7 @@
           <t>ORD-00028</t>
         </is>
       </c>
-      <c r="B494" s="4" t="n">
+      <c r="B494" s="3" t="n">
         <v>45958</v>
       </c>
       <c r="C494" t="inlineStr">
@@ -22999,7 +22987,7 @@
           <t>ORD-00524</t>
         </is>
       </c>
-      <c r="B495" s="4" t="n">
+      <c r="B495" s="3" t="n">
         <v>45959</v>
       </c>
       <c r="C495" t="inlineStr">
@@ -23044,7 +23032,7 @@
           <t>ORD-00302</t>
         </is>
       </c>
-      <c r="B496" s="4" t="n">
+      <c r="B496" s="3" t="n">
         <v>45959</v>
       </c>
       <c r="C496" t="inlineStr">
@@ -23089,7 +23077,7 @@
           <t>ORD-00433</t>
         </is>
       </c>
-      <c r="B497" s="4" t="n">
+      <c r="B497" s="3" t="n">
         <v>45959</v>
       </c>
       <c r="C497" t="inlineStr">
@@ -23134,7 +23122,7 @@
           <t>ORD-00482</t>
         </is>
       </c>
-      <c r="B498" s="4" t="n">
+      <c r="B498" s="3" t="n">
         <v>45960</v>
       </c>
       <c r="C498" t="inlineStr">
@@ -23179,7 +23167,7 @@
           <t>ORD-00334</t>
         </is>
       </c>
-      <c r="B499" s="4" t="n">
+      <c r="B499" s="3" t="n">
         <v>45960</v>
       </c>
       <c r="C499" t="inlineStr">
@@ -23224,7 +23212,7 @@
           <t>ORD-00553</t>
         </is>
       </c>
-      <c r="B500" s="4" t="n">
+      <c r="B500" s="3" t="n">
         <v>45960</v>
       </c>
       <c r="C500" t="inlineStr">
@@ -23269,7 +23257,7 @@
           <t>ORD-00038</t>
         </is>
       </c>
-      <c r="B501" s="4" t="n">
+      <c r="B501" s="3" t="n">
         <v>45960</v>
       </c>
       <c r="C501" t="inlineStr">
@@ -23314,7 +23302,7 @@
           <t>ORD-00388</t>
         </is>
       </c>
-      <c r="B502" s="4" t="n">
+      <c r="B502" s="3" t="n">
         <v>45961</v>
       </c>
       <c r="C502" t="inlineStr">
@@ -23359,7 +23347,7 @@
           <t>ORD-00101</t>
         </is>
       </c>
-      <c r="B503" s="4" t="n">
+      <c r="B503" s="3" t="n">
         <v>45961</v>
       </c>
       <c r="C503" t="inlineStr">
@@ -23404,7 +23392,7 @@
           <t>ORD-00084</t>
         </is>
       </c>
-      <c r="B504" s="4" t="n">
+      <c r="B504" s="3" t="n">
         <v>45961</v>
       </c>
       <c r="C504" t="inlineStr">
@@ -23449,7 +23437,7 @@
           <t>ORD-00090</t>
         </is>
       </c>
-      <c r="B505" s="4" t="n">
+      <c r="B505" s="3" t="n">
         <v>45961</v>
       </c>
       <c r="C505" t="inlineStr">
@@ -23494,7 +23482,7 @@
           <t>ORD-00545</t>
         </is>
       </c>
-      <c r="B506" s="4" t="n">
+      <c r="B506" s="3" t="n">
         <v>45961</v>
       </c>
       <c r="C506" t="inlineStr">
@@ -23539,7 +23527,7 @@
           <t>ORD-00582</t>
         </is>
       </c>
-      <c r="B507" s="4" t="n">
+      <c r="B507" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="C507" t="inlineStr">
@@ -23584,7 +23572,7 @@
           <t>ORD-00589</t>
         </is>
       </c>
-      <c r="B508" s="4" t="n">
+      <c r="B508" s="3" t="n">
         <v>45963</v>
       </c>
       <c r="C508" t="inlineStr">
@@ -23629,7 +23617,7 @@
           <t>ORD-00513</t>
         </is>
       </c>
-      <c r="B509" s="4" t="n">
+      <c r="B509" s="3" t="n">
         <v>45964</v>
       </c>
       <c r="C509" t="inlineStr">
@@ -23674,7 +23662,7 @@
           <t>ORD-00019</t>
         </is>
       </c>
-      <c r="B510" s="4" t="n">
+      <c r="B510" s="3" t="n">
         <v>45964</v>
       </c>
       <c r="C510" t="inlineStr">
@@ -23719,7 +23707,7 @@
           <t>ORD-00459</t>
         </is>
       </c>
-      <c r="B511" s="4" t="n">
+      <c r="B511" s="3" t="n">
         <v>45964</v>
       </c>
       <c r="C511" t="inlineStr">
@@ -23764,7 +23752,7 @@
           <t>ORD-00590</t>
         </is>
       </c>
-      <c r="B512" s="4" t="n">
+      <c r="B512" s="3" t="n">
         <v>45965</v>
       </c>
       <c r="C512" t="inlineStr">
@@ -23809,7 +23797,7 @@
           <t>ORD-00093</t>
         </is>
       </c>
-      <c r="B513" s="4" t="n">
+      <c r="B513" s="3" t="n">
         <v>45965</v>
       </c>
       <c r="C513" t="inlineStr">
@@ -23854,7 +23842,7 @@
           <t>ORD-00361</t>
         </is>
       </c>
-      <c r="B514" s="4" t="n">
+      <c r="B514" s="3" t="n">
         <v>45966</v>
       </c>
       <c r="C514" t="inlineStr">
@@ -23899,7 +23887,7 @@
           <t>ORD-00477</t>
         </is>
       </c>
-      <c r="B515" s="4" t="n">
+      <c r="B515" s="3" t="n">
         <v>45967</v>
       </c>
       <c r="C515" t="inlineStr">
@@ -23944,7 +23932,7 @@
           <t>ORD-00297</t>
         </is>
       </c>
-      <c r="B516" s="4" t="n">
+      <c r="B516" s="3" t="n">
         <v>45968</v>
       </c>
       <c r="C516" t="inlineStr">
@@ -23989,7 +23977,7 @@
           <t>ORD-00560</t>
         </is>
       </c>
-      <c r="B517" s="4" t="n">
+      <c r="B517" s="3" t="n">
         <v>45968</v>
       </c>
       <c r="C517" t="inlineStr">
@@ -24034,7 +24022,7 @@
           <t>ORD-00146</t>
         </is>
       </c>
-      <c r="B518" s="4" t="n">
+      <c r="B518" s="3" t="n">
         <v>45969</v>
       </c>
       <c r="C518" t="inlineStr">
@@ -24079,7 +24067,7 @@
           <t>ORD-00151</t>
         </is>
       </c>
-      <c r="B519" s="4" t="n">
+      <c r="B519" s="3" t="n">
         <v>45970</v>
       </c>
       <c r="C519" t="inlineStr">
@@ -24124,7 +24112,7 @@
           <t>ORD-00125</t>
         </is>
       </c>
-      <c r="B520" s="4" t="n">
+      <c r="B520" s="3" t="n">
         <v>45970</v>
       </c>
       <c r="C520" t="inlineStr">
@@ -24169,7 +24157,7 @@
           <t>ORD-00232</t>
         </is>
       </c>
-      <c r="B521" s="4" t="n">
+      <c r="B521" s="3" t="n">
         <v>45970</v>
       </c>
       <c r="C521" t="inlineStr">
@@ -24214,7 +24202,7 @@
           <t>ORD-00037</t>
         </is>
       </c>
-      <c r="B522" s="4" t="n">
+      <c r="B522" s="3" t="n">
         <v>45971</v>
       </c>
       <c r="C522" t="inlineStr">
@@ -24259,7 +24247,7 @@
           <t>ORD-00006</t>
         </is>
       </c>
-      <c r="B523" s="4" t="n">
+      <c r="B523" s="3" t="n">
         <v>45971</v>
       </c>
       <c r="C523" t="inlineStr">
@@ -24304,7 +24292,7 @@
           <t>ORD-00427</t>
         </is>
       </c>
-      <c r="B524" s="4" t="n">
+      <c r="B524" s="3" t="n">
         <v>45973</v>
       </c>
       <c r="C524" t="inlineStr">
@@ -24349,7 +24337,7 @@
           <t>ORD-00504</t>
         </is>
       </c>
-      <c r="B525" s="4" t="n">
+      <c r="B525" s="3" t="n">
         <v>45974</v>
       </c>
       <c r="C525" t="inlineStr">
@@ -24394,7 +24382,7 @@
           <t>ORD-00492</t>
         </is>
       </c>
-      <c r="B526" s="4" t="n">
+      <c r="B526" s="3" t="n">
         <v>45974</v>
       </c>
       <c r="C526" t="inlineStr">
@@ -24439,7 +24427,7 @@
           <t>ORD-00396</t>
         </is>
       </c>
-      <c r="B527" s="4" t="n">
+      <c r="B527" s="3" t="n">
         <v>45977</v>
       </c>
       <c r="C527" t="inlineStr">
@@ -24484,7 +24472,7 @@
           <t>ORD-00558</t>
         </is>
       </c>
-      <c r="B528" s="4" t="n">
+      <c r="B528" s="3" t="n">
         <v>45977</v>
       </c>
       <c r="C528" t="inlineStr">
@@ -24529,7 +24517,7 @@
           <t>ORD-00517</t>
         </is>
       </c>
-      <c r="B529" s="4" t="n">
+      <c r="B529" s="3" t="n">
         <v>45979</v>
       </c>
       <c r="C529" t="inlineStr">
@@ -24574,7 +24562,7 @@
           <t>ORD-00375</t>
         </is>
       </c>
-      <c r="B530" s="4" t="n">
+      <c r="B530" s="3" t="n">
         <v>45981</v>
       </c>
       <c r="C530" t="inlineStr">
@@ -24619,7 +24607,7 @@
           <t>ORD-00035</t>
         </is>
       </c>
-      <c r="B531" s="4" t="n">
+      <c r="B531" s="3" t="n">
         <v>45982</v>
       </c>
       <c r="C531" t="inlineStr">
@@ -24664,7 +24652,7 @@
           <t>ORD-00565</t>
         </is>
       </c>
-      <c r="B532" s="4" t="n">
+      <c r="B532" s="3" t="n">
         <v>45982</v>
       </c>
       <c r="C532" t="inlineStr">
@@ -24709,7 +24697,7 @@
           <t>ORD-00048</t>
         </is>
       </c>
-      <c r="B533" s="4" t="n">
+      <c r="B533" s="3" t="n">
         <v>45983</v>
       </c>
       <c r="C533" t="inlineStr">
@@ -24754,7 +24742,7 @@
           <t>ORD-00358</t>
         </is>
       </c>
-      <c r="B534" s="4" t="n">
+      <c r="B534" s="3" t="n">
         <v>45983</v>
       </c>
       <c r="C534" t="inlineStr">
@@ -24799,7 +24787,7 @@
           <t>ORD-00362</t>
         </is>
       </c>
-      <c r="B535" s="4" t="n">
+      <c r="B535" s="3" t="n">
         <v>45983</v>
       </c>
       <c r="C535" t="inlineStr">
@@ -24844,7 +24832,7 @@
           <t>ORD-00389</t>
         </is>
       </c>
-      <c r="B536" s="4" t="n">
+      <c r="B536" s="3" t="n">
         <v>45983</v>
       </c>
       <c r="C536" t="inlineStr">
@@ -24889,7 +24877,7 @@
           <t>ORD-00579</t>
         </is>
       </c>
-      <c r="B537" s="4" t="n">
+      <c r="B537" s="3" t="n">
         <v>45984</v>
       </c>
       <c r="C537" t="inlineStr">
@@ -24934,7 +24922,7 @@
           <t>ORD-00364</t>
         </is>
       </c>
-      <c r="B538" s="4" t="n">
+      <c r="B538" s="3" t="n">
         <v>45984</v>
       </c>
       <c r="C538" t="inlineStr">
@@ -24979,7 +24967,7 @@
           <t>ORD-00095</t>
         </is>
       </c>
-      <c r="B539" s="4" t="n">
+      <c r="B539" s="3" t="n">
         <v>45985</v>
       </c>
       <c r="C539" t="inlineStr">
@@ -25024,7 +25012,7 @@
           <t>ORD-00304</t>
         </is>
       </c>
-      <c r="B540" s="4" t="n">
+      <c r="B540" s="3" t="n">
         <v>45985</v>
       </c>
       <c r="C540" t="inlineStr">
@@ -25069,7 +25057,7 @@
           <t>ORD-00179</t>
         </is>
       </c>
-      <c r="B541" s="4" t="n">
+      <c r="B541" s="3" t="n">
         <v>45986</v>
       </c>
       <c r="C541" t="inlineStr">
@@ -25114,7 +25102,7 @@
           <t>ORD-00592</t>
         </is>
       </c>
-      <c r="B542" s="4" t="n">
+      <c r="B542" s="3" t="n">
         <v>45987</v>
       </c>
       <c r="C542" t="inlineStr">
@@ -25159,7 +25147,7 @@
           <t>ORD-00220</t>
         </is>
       </c>
-      <c r="B543" s="4" t="n">
+      <c r="B543" s="3" t="n">
         <v>45987</v>
       </c>
       <c r="C543" t="inlineStr">
@@ -25204,7 +25192,7 @@
           <t>ORD-00067</t>
         </is>
       </c>
-      <c r="B544" s="4" t="n">
+      <c r="B544" s="3" t="n">
         <v>45988</v>
       </c>
       <c r="C544" t="inlineStr">
@@ -25249,7 +25237,7 @@
           <t>ORD-00345</t>
         </is>
       </c>
-      <c r="B545" s="4" t="n">
+      <c r="B545" s="3" t="n">
         <v>45988</v>
       </c>
       <c r="C545" t="inlineStr">
@@ -25294,7 +25282,7 @@
           <t>ORD-00202</t>
         </is>
       </c>
-      <c r="B546" s="4" t="n">
+      <c r="B546" s="3" t="n">
         <v>45989</v>
       </c>
       <c r="C546" t="inlineStr">
@@ -25339,7 +25327,7 @@
           <t>ORD-00529</t>
         </is>
       </c>
-      <c r="B547" s="4" t="n">
+      <c r="B547" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="C547" t="inlineStr">
@@ -25384,7 +25372,7 @@
           <t>ORD-00153</t>
         </is>
       </c>
-      <c r="B548" s="4" t="n">
+      <c r="B548" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="C548" t="inlineStr">
@@ -25429,7 +25417,7 @@
           <t>ORD-00324</t>
         </is>
       </c>
-      <c r="B549" s="4" t="n">
+      <c r="B549" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="C549" t="inlineStr">
@@ -25474,7 +25462,7 @@
           <t>ORD-00530</t>
         </is>
       </c>
-      <c r="B550" s="4" t="n">
+      <c r="B550" s="3" t="n">
         <v>45994</v>
       </c>
       <c r="C550" t="inlineStr">
@@ -25519,7 +25507,7 @@
           <t>ORD-00061</t>
         </is>
       </c>
-      <c r="B551" s="4" t="n">
+      <c r="B551" s="3" t="n">
         <v>45994</v>
       </c>
       <c r="C551" t="inlineStr">
@@ -25564,7 +25552,7 @@
           <t>ORD-00586</t>
         </is>
       </c>
-      <c r="B552" s="4" t="n">
+      <c r="B552" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="C552" t="inlineStr">
@@ -25609,7 +25597,7 @@
           <t>ORD-00577</t>
         </is>
       </c>
-      <c r="B553" s="4" t="n">
+      <c r="B553" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="C553" t="inlineStr">
@@ -25654,7 +25642,7 @@
           <t>ORD-00264</t>
         </is>
       </c>
-      <c r="B554" s="4" t="n">
+      <c r="B554" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="C554" t="inlineStr">
@@ -25699,7 +25687,7 @@
           <t>ORD-00452</t>
         </is>
       </c>
-      <c r="B555" s="4" t="n">
+      <c r="B555" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="C555" t="inlineStr">
@@ -25744,7 +25732,7 @@
           <t>ORD-00527</t>
         </is>
       </c>
-      <c r="B556" s="4" t="n">
+      <c r="B556" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="C556" t="inlineStr">
@@ -25789,7 +25777,7 @@
           <t>ORD-00438</t>
         </is>
       </c>
-      <c r="B557" s="4" t="n">
+      <c r="B557" s="3" t="n">
         <v>45996</v>
       </c>
       <c r="C557" t="inlineStr">
@@ -25834,7 +25822,7 @@
           <t>ORD-00499</t>
         </is>
       </c>
-      <c r="B558" s="4" t="n">
+      <c r="B558" s="3" t="n">
         <v>45996</v>
       </c>
       <c r="C558" t="inlineStr">
@@ -25879,7 +25867,7 @@
           <t>ORD-00024</t>
         </is>
       </c>
-      <c r="B559" s="4" t="n">
+      <c r="B559" s="3" t="n">
         <v>45996</v>
       </c>
       <c r="C559" t="inlineStr">
@@ -25924,7 +25912,7 @@
           <t>ORD-00421</t>
         </is>
       </c>
-      <c r="B560" s="4" t="n">
+      <c r="B560" s="3" t="n">
         <v>45996</v>
       </c>
       <c r="C560" t="inlineStr">
@@ -25969,7 +25957,7 @@
           <t>ORD-00470</t>
         </is>
       </c>
-      <c r="B561" s="4" t="n">
+      <c r="B561" s="3" t="n">
         <v>45998</v>
       </c>
       <c r="C561" t="inlineStr">
@@ -26014,7 +26002,7 @@
           <t>ORD-00491</t>
         </is>
       </c>
-      <c r="B562" s="4" t="n">
+      <c r="B562" s="3" t="n">
         <v>45998</v>
       </c>
       <c r="C562" t="inlineStr">
@@ -26059,7 +26047,7 @@
           <t>ORD-00382</t>
         </is>
       </c>
-      <c r="B563" s="4" t="n">
+      <c r="B563" s="3" t="n">
         <v>45999</v>
       </c>
       <c r="C563" t="inlineStr">
@@ -26104,7 +26092,7 @@
           <t>ORD-00409</t>
         </is>
       </c>
-      <c r="B564" s="4" t="n">
+      <c r="B564" s="3" t="n">
         <v>45999</v>
       </c>
       <c r="C564" t="inlineStr">
@@ -26149,7 +26137,7 @@
           <t>ORD-00348</t>
         </is>
       </c>
-      <c r="B565" s="4" t="n">
+      <c r="B565" s="3" t="n">
         <v>45999</v>
       </c>
       <c r="C565" t="inlineStr">
@@ -26194,7 +26182,7 @@
           <t>ORD-00319</t>
         </is>
       </c>
-      <c r="B566" s="4" t="n">
+      <c r="B566" s="3" t="n">
         <v>46000</v>
       </c>
       <c r="C566" t="inlineStr">
@@ -26239,7 +26227,7 @@
           <t>ORD-00286</t>
         </is>
       </c>
-      <c r="B567" s="4" t="n">
+      <c r="B567" s="3" t="n">
         <v>46000</v>
       </c>
       <c r="C567" t="inlineStr">
@@ -26284,7 +26272,7 @@
           <t>ORD-00181</t>
         </is>
       </c>
-      <c r="B568" s="4" t="n">
+      <c r="B568" s="3" t="n">
         <v>46000</v>
       </c>
       <c r="C568" t="inlineStr">
@@ -26329,7 +26317,7 @@
           <t>ORD-00081</t>
         </is>
       </c>
-      <c r="B569" s="4" t="n">
+      <c r="B569" s="3" t="n">
         <v>46001</v>
       </c>
       <c r="C569" t="inlineStr">
@@ -26374,7 +26362,7 @@
           <t>ORD-00383</t>
         </is>
       </c>
-      <c r="B570" s="4" t="n">
+      <c r="B570" s="3" t="n">
         <v>46003</v>
       </c>
       <c r="C570" t="inlineStr">
@@ -26419,7 +26407,7 @@
           <t>ORD-00571</t>
         </is>
       </c>
-      <c r="B571" s="4" t="n">
+      <c r="B571" s="3" t="n">
         <v>46004</v>
       </c>
       <c r="C571" t="inlineStr">
@@ -26464,7 +26452,7 @@
           <t>ORD-00340</t>
         </is>
       </c>
-      <c r="B572" s="4" t="n">
+      <c r="B572" s="3" t="n">
         <v>46005</v>
       </c>
       <c r="C572" t="inlineStr">
@@ -26509,7 +26497,7 @@
           <t>ORD-00448</t>
         </is>
       </c>
-      <c r="B573" s="4" t="n">
+      <c r="B573" s="3" t="n">
         <v>46006</v>
       </c>
       <c r="C573" t="inlineStr">
@@ -26554,7 +26542,7 @@
           <t>ORD-00293</t>
         </is>
       </c>
-      <c r="B574" s="4" t="n">
+      <c r="B574" s="3" t="n">
         <v>46006</v>
       </c>
       <c r="C574" t="inlineStr">
@@ -26599,7 +26587,7 @@
           <t>ORD-00274</t>
         </is>
       </c>
-      <c r="B575" s="4" t="n">
+      <c r="B575" s="3" t="n">
         <v>46007</v>
       </c>
       <c r="C575" t="inlineStr">
@@ -26644,7 +26632,7 @@
           <t>ORD-00195</t>
         </is>
       </c>
-      <c r="B576" s="4" t="n">
+      <c r="B576" s="3" t="n">
         <v>46008</v>
       </c>
       <c r="C576" t="inlineStr">
@@ -26689,7 +26677,7 @@
           <t>ORD-00515</t>
         </is>
       </c>
-      <c r="B577" s="4" t="n">
+      <c r="B577" s="3" t="n">
         <v>46008</v>
       </c>
       <c r="C577" t="inlineStr">
@@ -26734,7 +26722,7 @@
           <t>ORD-00451</t>
         </is>
       </c>
-      <c r="B578" s="4" t="n">
+      <c r="B578" s="3" t="n">
         <v>46008</v>
       </c>
       <c r="C578" t="inlineStr">
@@ -26779,7 +26767,7 @@
           <t>ORD-00337</t>
         </is>
       </c>
-      <c r="B579" s="4" t="n">
+      <c r="B579" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="C579" t="inlineStr">
@@ -26824,7 +26812,7 @@
           <t>ORD-00503</t>
         </is>
       </c>
-      <c r="B580" s="4" t="n">
+      <c r="B580" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="C580" t="inlineStr">
@@ -26869,7 +26857,7 @@
           <t>ORD-00200</t>
         </is>
       </c>
-      <c r="B581" s="4" t="n">
+      <c r="B581" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="C581" t="inlineStr">
@@ -26914,7 +26902,7 @@
           <t>ORD-00466</t>
         </is>
       </c>
-      <c r="B582" s="4" t="n">
+      <c r="B582" s="3" t="n">
         <v>46010</v>
       </c>
       <c r="C582" t="inlineStr">
@@ -26959,7 +26947,7 @@
           <t>ORD-00417</t>
         </is>
       </c>
-      <c r="B583" s="4" t="n">
+      <c r="B583" s="3" t="n">
         <v>46011</v>
       </c>
       <c r="C583" t="inlineStr">
@@ -27004,7 +26992,7 @@
           <t>ORD-00064</t>
         </is>
       </c>
-      <c r="B584" s="4" t="n">
+      <c r="B584" s="3" t="n">
         <v>46011</v>
       </c>
       <c r="C584" t="inlineStr">
@@ -27049,7 +27037,7 @@
           <t>ORD-00208</t>
         </is>
       </c>
-      <c r="B585" s="4" t="n">
+      <c r="B585" s="3" t="n">
         <v>46011</v>
       </c>
       <c r="C585" t="inlineStr">
@@ -27094,7 +27082,7 @@
           <t>ORD-00355</t>
         </is>
       </c>
-      <c r="B586" s="4" t="n">
+      <c r="B586" s="3" t="n">
         <v>46011</v>
       </c>
       <c r="C586" t="inlineStr">
@@ -27139,7 +27127,7 @@
           <t>ORD-00404</t>
         </is>
       </c>
-      <c r="B587" s="4" t="n">
+      <c r="B587" s="3" t="n">
         <v>46012</v>
       </c>
       <c r="C587" t="inlineStr">
@@ -27184,7 +27172,7 @@
           <t>ORD-00046</t>
         </is>
       </c>
-      <c r="B588" s="4" t="n">
+      <c r="B588" s="3" t="n">
         <v>46012</v>
       </c>
       <c r="C588" t="inlineStr">
@@ -27229,7 +27217,7 @@
           <t>ORD-00325</t>
         </is>
       </c>
-      <c r="B589" s="4" t="n">
+      <c r="B589" s="3" t="n">
         <v>46013</v>
       </c>
       <c r="C589" t="inlineStr">
@@ -27274,7 +27262,7 @@
           <t>ORD-00441</t>
         </is>
       </c>
-      <c r="B590" s="4" t="n">
+      <c r="B590" s="3" t="n">
         <v>46013</v>
       </c>
       <c r="C590" t="inlineStr">
@@ -27319,7 +27307,7 @@
           <t>ORD-00012</t>
         </is>
       </c>
-      <c r="B591" s="4" t="n">
+      <c r="B591" s="3" t="n">
         <v>46014</v>
       </c>
       <c r="C591" t="inlineStr">
@@ -27364,7 +27352,7 @@
           <t>ORD-00594</t>
         </is>
       </c>
-      <c r="B592" s="4" t="n">
+      <c r="B592" s="3" t="n">
         <v>46015</v>
       </c>
       <c r="C592" t="inlineStr">
@@ -27409,7 +27397,7 @@
           <t>ORD-00141</t>
         </is>
       </c>
-      <c r="B593" s="4" t="n">
+      <c r="B593" s="3" t="n">
         <v>46016</v>
       </c>
       <c r="C593" t="inlineStr">
@@ -27454,7 +27442,7 @@
           <t>ORD-00555</t>
         </is>
       </c>
-      <c r="B594" s="4" t="n">
+      <c r="B594" s="3" t="n">
         <v>46017</v>
       </c>
       <c r="C594" t="inlineStr">
@@ -27499,7 +27487,7 @@
           <t>ORD-00265</t>
         </is>
       </c>
-      <c r="B595" s="4" t="n">
+      <c r="B595" s="3" t="n">
         <v>46019</v>
       </c>
       <c r="C595" t="inlineStr">
@@ -27544,7 +27532,7 @@
           <t>ORD-00347</t>
         </is>
       </c>
-      <c r="B596" s="4" t="n">
+      <c r="B596" s="3" t="n">
         <v>46019</v>
       </c>
       <c r="C596" t="inlineStr">
@@ -27589,7 +27577,7 @@
           <t>ORD-00145</t>
         </is>
       </c>
-      <c r="B597" s="4" t="n">
+      <c r="B597" s="3" t="n">
         <v>46020</v>
       </c>
       <c r="C597" t="inlineStr">
@@ -27634,7 +27622,7 @@
           <t>ORD-00356</t>
         </is>
       </c>
-      <c r="B598" s="4" t="n">
+      <c r="B598" s="3" t="n">
         <v>46020</v>
       </c>
       <c r="C598" t="inlineStr">
@@ -27679,7 +27667,7 @@
           <t>ORD-00511</t>
         </is>
       </c>
-      <c r="B599" s="4" t="n">
+      <c r="B599" s="3" t="n">
         <v>46021</v>
       </c>
       <c r="C599" t="inlineStr">
@@ -27724,7 +27712,7 @@
           <t>ORD-00161</t>
         </is>
       </c>
-      <c r="B600" s="4" t="n">
+      <c r="B600" s="3" t="n">
         <v>46021</v>
       </c>
       <c r="C600" t="inlineStr">
@@ -27769,7 +27757,7 @@
           <t>ORD-00401</t>
         </is>
       </c>
-      <c r="B601" s="4" t="n">
+      <c r="B601" s="3" t="n">
         <v>46022</v>
       </c>
       <c r="C601" t="inlineStr">
@@ -27830,22 +27818,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Total_Sales</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Total_Profit</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
@@ -27954,22 +27942,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Total_Sales</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Total_Profit</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Units_Sold</t>
         </is>
@@ -28044,17 +28032,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Total_Sales</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Total_Profit</t>
         </is>
